--- a/PRIZEPICKS_HITTER_AI_V6_TOP30_2026_07_24.xlsx
+++ b/PRIZEPICKS_HITTER_AI_V6_TOP30_2026_07_24.xlsx
@@ -2232,13 +2232,13 @@
         <v>13.39</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>12.61</v>
+        <v>12.63</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>12.61</v>
+        <v>12.63</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>10.26</v>
+        <v>10.27</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>9.119999999999999</v>
@@ -2247,13 +2247,13 @@
         <v>8.09</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>9</v>
+        <v>9.01</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>8.09</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.899</v>
+        <v>0.898</v>
       </c>
       <c r="S2" s="3" t="n">
         <v>14.8</v>
@@ -2301,10 +2301,10 @@
         <v>87.09999999999999</v>
       </c>
       <c r="AF2" s="5" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="AG2" s="5" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="AH2" s="5" t="n">
         <v>74.8</v>
@@ -2313,31 +2313,31 @@
         <v>74.3</v>
       </c>
       <c r="AJ2" s="5" t="n">
-        <v>65.7</v>
+        <v>65.8</v>
       </c>
       <c r="AK2" s="5" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="AL2" s="5" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="AM2" s="6" t="n">
-        <v>54</v>
+        <v>54.2</v>
       </c>
       <c r="AN2" s="7" t="n">
-        <v>54</v>
+        <v>54.2</v>
       </c>
       <c r="AO2" s="7" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="AP2" s="7" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="AQ2" s="7" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="AR2" s="7" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="AS2" s="7" t="n">
         <v>41.9</v>
@@ -2361,7 +2361,7 @@
         <v>33.5</v>
       </c>
       <c r="AZ2" s="3" t="n">
-        <v>301.46</v>
+        <v>301.73</v>
       </c>
       <c r="BA2" s="4" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="BB2" s="9" t="inlineStr">
         <is>
-          <t>MORE 9.0 | 59.1% | Edge +3.6</t>
+          <t>MORE 9.0 | 59.2% | Edge +3.6</t>
         </is>
       </c>
       <c r="BC2" s="4" t="inlineStr">
@@ -2382,13 +2382,13 @@
         <v>9</v>
       </c>
       <c r="BE2" s="3" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="BF2" s="3" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="BG2" s="3" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="BH2" s="4" t="inlineStr">
         <is>
@@ -2900,13 +2900,13 @@
         <v>8.09</v>
       </c>
       <c r="HK2" s="3" t="n">
-        <v>6.67</v>
+        <v>6.68</v>
       </c>
       <c r="HL2" s="3" t="n">
         <v>17.45</v>
       </c>
       <c r="HM2" s="3" t="n">
-        <v>23.75</v>
+        <v>23.73</v>
       </c>
       <c r="HN2" s="3" t="n">
         <v>4.39</v>
@@ -2946,10 +2946,10 @@
         <v>83.3</v>
       </c>
       <c r="HY2" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="HZ2" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="IA2" s="3" t="n">
         <v>71.8</v>
@@ -2958,31 +2958,31 @@
         <v>71.8</v>
       </c>
       <c r="IC2" s="3" t="n">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
       <c r="ID2" s="3" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="IE2" s="3" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="IF2" s="3" t="n">
-        <v>54</v>
+        <v>54.2</v>
       </c>
       <c r="IG2" s="3" t="n">
-        <v>54</v>
+        <v>54.2</v>
       </c>
       <c r="IH2" s="3" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="II2" s="3" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="IJ2" s="3" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="IK2" s="3" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="IL2" s="3" t="n">
         <v>41.9</v>
@@ -3243,11 +3243,11 @@
       <c r="AS3" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="AT3" s="8" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="AU3" s="8" t="n">
-        <v>39.9</v>
+      <c r="AT3" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU3" s="7" t="n">
+        <v>40</v>
       </c>
       <c r="AV3" s="8" t="n">
         <v>35.2</v>
@@ -3889,10 +3889,10 @@
         <v>42</v>
       </c>
       <c r="IM3" s="3" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="IN3" s="3" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="IO3" s="3" t="n">
         <v>35.2</v>
@@ -4034,10 +4034,10 @@
         <v>12.18</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>11.81</v>
+        <v>11.82</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>11.81</v>
+        <v>11.82</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>9.289999999999999</v>
@@ -4049,13 +4049,13 @@
         <v>8.359999999999999</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>9.32</v>
+        <v>9.33</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>8.359999999999999</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.897</v>
+        <v>0.896</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>8.800000000000001</v>
@@ -4103,16 +4103,16 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AF4" s="5" t="n">
-        <v>72.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="AG4" s="5" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="AH4" s="5" t="n">
-        <v>67.7</v>
+        <v>67.8</v>
       </c>
       <c r="AI4" s="5" t="n">
-        <v>59.9</v>
+        <v>67.3</v>
       </c>
       <c r="AJ4" s="5" t="n">
         <v>58.4</v>
@@ -4139,31 +4139,31 @@
         <v>41.2</v>
       </c>
       <c r="AR4" s="8" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="AS4" s="8" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="AT4" s="8" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="AU4" s="8" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="AV4" s="8" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="AW4" s="8" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="AX4" s="8" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="AY4" s="8" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="AZ4" s="3" t="n">
-        <v>276.98</v>
+        <v>278.02</v>
       </c>
       <c r="BA4" s="4" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>58.4</v>
       </c>
       <c r="BF4" s="3" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="BG4" s="3" t="n">
         <v>16.8</v>
@@ -4702,13 +4702,13 @@
         <v>8.359999999999999</v>
       </c>
       <c r="HK4" s="3" t="n">
-        <v>5.7</v>
+        <v>5.71</v>
       </c>
       <c r="HL4" s="3" t="n">
         <v>17.36</v>
       </c>
       <c r="HM4" s="3" t="n">
-        <v>23.64</v>
+        <v>23.63</v>
       </c>
       <c r="HN4" s="3" t="n">
         <v>4.4</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="HQ4" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="HR4" s="3" t="n">
@@ -4748,16 +4748,16 @@
         <v>77.09999999999999</v>
       </c>
       <c r="HY4" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="HZ4" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="IA4" s="3" t="n">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
       <c r="IB4" s="3" t="n">
-        <v>57.4</v>
+        <v>64.8</v>
       </c>
       <c r="IC4" s="3" t="n">
         <v>57.4</v>
@@ -4784,28 +4784,28 @@
         <v>41.2</v>
       </c>
       <c r="IK4" s="3" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="IL4" s="3" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="IM4" s="3" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="IN4" s="3" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="IO4" s="3" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="IP4" s="3" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="IQ4" s="3" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="IR4" s="3" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="IS4" s="3" t="n">
         <v>2.6</v>
@@ -5836,10 +5836,10 @@
         <v>11.69</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>11.22</v>
+        <v>11.23</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>11.22</v>
+        <v>11.23</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>9.48</v>
@@ -5857,7 +5857,7 @@
         <v>6.81</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>8.800000000000001</v>
@@ -5890,7 +5890,7 @@
         <v>96</v>
       </c>
       <c r="AA6" s="5" t="n">
-        <v>95.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AB6" s="5" t="n">
         <v>91.3</v>
@@ -5908,10 +5908,10 @@
         <v>80.59999999999999</v>
       </c>
       <c r="AG6" s="5" t="n">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AH6" s="5" t="n">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AI6" s="5" t="n">
         <v>67.5</v>
@@ -5932,10 +5932,10 @@
         <v>47.5</v>
       </c>
       <c r="AO6" s="7" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="AP6" s="7" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="AQ6" s="8" t="n">
         <v>39.8</v>
@@ -5965,7 +5965,7 @@
         <v>24.7</v>
       </c>
       <c r="AZ6" s="3" t="n">
-        <v>273.08</v>
+        <v>273.23</v>
       </c>
       <c r="BA6" s="4" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>58.3</v>
       </c>
       <c r="BF6" s="3" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="BG6" s="3" t="n">
         <v>16.6</v>
@@ -6512,13 +6512,13 @@
         <v>6.81</v>
       </c>
       <c r="HK6" s="3" t="n">
-        <v>6.33</v>
+        <v>6.34</v>
       </c>
       <c r="HL6" s="3" t="n">
         <v>14.98</v>
       </c>
       <c r="HM6" s="3" t="n">
-        <v>20.48</v>
+        <v>20.47</v>
       </c>
       <c r="HN6" s="3" t="n">
         <v>4.61</v>
@@ -6537,13 +6537,13 @@
         </is>
       </c>
       <c r="HR6" s="3" t="n">
-        <v>93.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="HS6" s="3" t="n">
-        <v>93.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="HT6" s="3" t="n">
-        <v>93.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="HU6" s="3" t="n">
         <v>86.59999999999999</v>
@@ -6561,10 +6561,10 @@
         <v>76.59999999999999</v>
       </c>
       <c r="HZ6" s="3" t="n">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="IA6" s="3" t="n">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="IB6" s="3" t="n">
         <v>65</v>
@@ -6585,10 +6585,10 @@
         <v>47.5</v>
       </c>
       <c r="IH6" s="3" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="II6" s="3" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="IJ6" s="3" t="n">
         <v>39.8</v>
@@ -6618,10 +6618,10 @@
         <v>24.7</v>
       </c>
       <c r="IS6" s="3" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="IT6" s="3" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="IU6" s="3" t="n">
         <v>2.5</v>
@@ -7654,10 +7654,10 @@
         <v>11.26</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10.74</v>
+        <v>10.75</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>10.74</v>
+        <v>10.75</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>8.380000000000001</v>
@@ -7669,13 +7669,13 @@
         <v>7.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>8.93</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>7.7</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.862</v>
+        <v>0.861</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>5.4</v>
@@ -7744,10 +7744,10 @@
         <v>49.7</v>
       </c>
       <c r="AM8" s="7" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="AN8" s="7" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="AO8" s="7" t="n">
         <v>41.2</v>
@@ -7765,25 +7765,25 @@
         <v>35.5</v>
       </c>
       <c r="AT8" s="8" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="AU8" s="8" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="AV8" s="8" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="AW8" s="8" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="AX8" s="8" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="AY8" s="8" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AZ8" s="3" t="n">
-        <v>270.5</v>
+        <v>270.63</v>
       </c>
       <c r="BA8" s="4" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>63.2</v>
       </c>
       <c r="BF8" s="3" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="BG8" s="3" t="n">
         <v>26.4</v>
@@ -8330,13 +8330,13 @@
         <v>7.7</v>
       </c>
       <c r="HK8" s="3" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="HL8" s="3" t="n">
         <v>15.27</v>
       </c>
       <c r="HM8" s="3" t="n">
-        <v>21.31</v>
+        <v>21.29</v>
       </c>
       <c r="HN8" s="3" t="n">
         <v>4.54</v>
@@ -8397,10 +8397,10 @@
         <v>49.7</v>
       </c>
       <c r="IF8" s="3" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="IG8" s="3" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="IH8" s="3" t="n">
         <v>41.2</v>
@@ -8418,22 +8418,22 @@
         <v>35.5</v>
       </c>
       <c r="IM8" s="3" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="IN8" s="3" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="IO8" s="3" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="IP8" s="3" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="IQ8" s="3" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="IR8" s="3" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="IS8" s="3" t="n">
         <v>4.2</v>
@@ -8578,13 +8578,13 @@
         <v>7.07</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>7.68</v>
+        <v>7.69</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>7.07</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.92</v>
+        <v>0.919</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>5.4</v>
@@ -8611,13 +8611,13 @@
         </is>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="Z9" s="5" t="n">
         <v>93.3</v>
       </c>
       <c r="AA9" s="5" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="AB9" s="5" t="n">
         <v>88.7</v>
@@ -8626,7 +8626,7 @@
         <v>87.8</v>
       </c>
       <c r="AD9" s="5" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="AE9" s="5" t="n">
         <v>74.7</v>
@@ -8641,10 +8641,10 @@
         <v>70.09999999999999</v>
       </c>
       <c r="AI9" s="5" t="n">
-        <v>62.5</v>
+        <v>62.4</v>
       </c>
       <c r="AJ9" s="5" t="n">
-        <v>61</v>
+        <v>60.9</v>
       </c>
       <c r="AK9" s="6" t="n">
         <v>53.9</v>
@@ -8659,7 +8659,7 @@
         <v>49.3</v>
       </c>
       <c r="AO9" s="7" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="AP9" s="8" t="n">
         <v>39.3</v>
@@ -8668,16 +8668,16 @@
         <v>39.3</v>
       </c>
       <c r="AR9" s="8" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="AS9" s="8" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="AT9" s="8" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="AU9" s="8" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="AV9" s="8" t="n">
         <v>26.6</v>
@@ -8692,7 +8692,7 @@
         <v>23.6</v>
       </c>
       <c r="AZ9" s="3" t="n">
-        <v>267.56</v>
+        <v>267.55</v>
       </c>
       <c r="BA9" s="4" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="BB9" s="9" t="inlineStr">
         <is>
-          <t>MORE 8.0 | 61.0% | Edge +2.7</t>
+          <t>MORE 8.0 | 60.9% | Edge +2.7</t>
         </is>
       </c>
       <c r="BC9" s="4" t="inlineStr">
@@ -8713,13 +8713,13 @@
         <v>8</v>
       </c>
       <c r="BE9" s="3" t="n">
-        <v>61</v>
+        <v>60.9</v>
       </c>
       <c r="BF9" s="3" t="n">
         <v>2.71</v>
       </c>
       <c r="BG9" s="3" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="BH9" s="4" t="inlineStr">
         <is>
@@ -9234,13 +9234,13 @@
         <v>5.46</v>
       </c>
       <c r="HL9" s="3" t="n">
-        <v>14.66</v>
+        <v>14.65</v>
       </c>
       <c r="HM9" s="3" t="n">
-        <v>20.18</v>
+        <v>20.17</v>
       </c>
       <c r="HN9" s="3" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="HO9" s="3" t="n">
         <v>0</v>
@@ -9256,13 +9256,13 @@
         </is>
       </c>
       <c r="HR9" s="3" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="HS9" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="HT9" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="HU9" s="3" t="n">
         <v>82.59999999999999</v>
@@ -9271,7 +9271,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="HW9" s="3" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="HX9" s="3" t="n">
         <v>70.2</v>
@@ -9286,10 +9286,10 @@
         <v>67.09999999999999</v>
       </c>
       <c r="IB9" s="3" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="IC9" s="3" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="ID9" s="3" t="n">
         <v>53.9</v>
@@ -9304,7 +9304,7 @@
         <v>49.3</v>
       </c>
       <c r="IH9" s="3" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="II9" s="3" t="n">
         <v>39.3</v>
@@ -9313,16 +9313,16 @@
         <v>39.3</v>
       </c>
       <c r="IK9" s="3" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="IL9" s="3" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="IM9" s="3" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="IN9" s="3" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="IO9" s="3" t="n">
         <v>26.6</v>
@@ -9340,7 +9340,7 @@
         <v>2.8</v>
       </c>
       <c r="IT9" s="3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="IU9" s="3" t="n">
         <v>4.2</v>
@@ -9464,10 +9464,10 @@
         <v>11.43</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>11.38</v>
+        <v>11.39</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>11.38</v>
+        <v>11.39</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>9.550000000000001</v>
@@ -9479,13 +9479,13 @@
         <v>7</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>9.1</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>7</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>9.6</v>
@@ -9524,13 +9524,13 @@
         <v>94.2</v>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>89.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="AD10" s="5" t="n">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="AE10" s="5" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="AF10" s="5" t="n">
         <v>79.3</v>
@@ -9551,10 +9551,10 @@
         <v>57.6</v>
       </c>
       <c r="AL10" s="7" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="AM10" s="7" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="AN10" s="7" t="n">
         <v>48.5</v>
@@ -9569,31 +9569,31 @@
         <v>41.4</v>
       </c>
       <c r="AR10" s="8" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="AS10" s="8" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="AT10" s="8" t="n">
         <v>36</v>
       </c>
       <c r="AU10" s="8" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="AV10" s="8" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="AW10" s="8" t="n">
         <v>29.8</v>
       </c>
       <c r="AX10" s="8" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="AY10" s="8" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>265.91</v>
+        <v>266.05</v>
       </c>
       <c r="BA10" s="4" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>65.7</v>
       </c>
       <c r="BF10" s="3" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="BG10" s="3" t="n">
         <v>31.4</v>
@@ -10140,13 +10140,13 @@
         <v>7</v>
       </c>
       <c r="HK10" s="3" t="n">
-        <v>6.47</v>
+        <v>6.48</v>
       </c>
       <c r="HL10" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="HM10" s="3" t="n">
-        <v>21.09</v>
+        <v>21.08</v>
       </c>
       <c r="HN10" s="3" t="n">
         <v>4.51</v>
@@ -10177,13 +10177,13 @@
         <v>91</v>
       </c>
       <c r="HV10" s="3" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="HW10" s="3" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="HX10" s="3" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="HY10" s="3" t="n">
         <v>75.3</v>
@@ -10204,10 +10204,10 @@
         <v>57.6</v>
       </c>
       <c r="IE10" s="3" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="IF10" s="3" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="IG10" s="3" t="n">
         <v>48.5</v>
@@ -10222,28 +10222,28 @@
         <v>41.4</v>
       </c>
       <c r="IK10" s="3" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="IL10" s="3" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="IM10" s="3" t="n">
         <v>36</v>
       </c>
       <c r="IN10" s="3" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="IO10" s="3" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="IP10" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="IQ10" s="3" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="IR10" s="3" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="IS10" s="3" t="n">
         <v>0</v>
@@ -10373,13 +10373,13 @@
         <v>10.95</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.88</v>
+        <v>10.9</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>10.88</v>
+        <v>10.9</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>9.24</v>
+        <v>9.25</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>8.48</v>
@@ -10388,13 +10388,13 @@
         <v>7.64</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>8.77</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>7.64</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.872</v>
+        <v>0.87</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>5.6</v>
@@ -10427,67 +10427,67 @@
         <v>94.40000000000001</v>
       </c>
       <c r="AA11" s="5" t="n">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AB11" s="5" t="n">
-        <v>89.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="AD11" s="5" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AE11" s="5" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AF11" s="5" t="n">
-        <v>70.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AG11" s="5" t="n">
-        <v>69.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AH11" s="5" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="AI11" s="6" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="AJ11" s="7" t="n">
-        <v>56.2</v>
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AI11" s="5" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AJ11" s="6" t="n">
+        <v>56.3</v>
       </c>
       <c r="AK11" s="7" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="AL11" s="7" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="AM11" s="7" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="AN11" s="7" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="AO11" s="7" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
       <c r="AP11" s="8" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="AQ11" s="8" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="AR11" s="8" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="AS11" s="8" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="AT11" s="8" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="AU11" s="8" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="AV11" s="8" t="n">
         <v>28.6</v>
@@ -10499,10 +10499,10 @@
         <v>27.2</v>
       </c>
       <c r="AY11" s="8" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AZ11" s="3" t="n">
-        <v>261.72</v>
+        <v>263.01</v>
       </c>
       <c r="BA11" s="4" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="BB11" s="9" t="inlineStr">
         <is>
-          <t>MORE 7.0 | 66.3% | Edge +3.9</t>
+          <t>MORE 7.5 | 65.9% | Edge +3.4</t>
         </is>
       </c>
       <c r="BC11" s="4" t="inlineStr">
@@ -10520,16 +10520,16 @@
         </is>
       </c>
       <c r="BD11" s="3" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BE11" s="3" t="n">
-        <v>66.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="BF11" s="3" t="n">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="BG11" s="3" t="n">
-        <v>32.6</v>
+        <v>31.8</v>
       </c>
       <c r="BH11" s="4" t="inlineStr">
         <is>
@@ -11049,13 +11049,13 @@
         <v>7.64</v>
       </c>
       <c r="HK11" s="3" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="HL11" s="3" t="n">
         <v>15.34</v>
       </c>
       <c r="HM11" s="3" t="n">
-        <v>21.44</v>
+        <v>21.43</v>
       </c>
       <c r="HN11" s="3" t="n">
         <v>4.43</v>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="HQ11" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="HR11" s="3" t="n">
@@ -11080,67 +11080,67 @@
         <v>90.7</v>
       </c>
       <c r="HT11" s="3" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="HU11" s="3" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="HV11" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="HW11" s="3" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="HX11" s="3" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="HY11" s="3" t="n">
-        <v>66.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="HZ11" s="3" t="n">
-        <v>66.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="IA11" s="3" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
       <c r="IB11" s="3" t="n">
-        <v>55.2</v>
+        <v>63.4</v>
       </c>
       <c r="IC11" s="3" t="n">
-        <v>55.2</v>
+        <v>55.3</v>
       </c>
       <c r="ID11" s="3" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="IE11" s="3" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="IF11" s="3" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="IG11" s="3" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="IH11" s="3" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
       <c r="II11" s="3" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="IJ11" s="3" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="IK11" s="3" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="IL11" s="3" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="IM11" s="3" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="IN11" s="3" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="IO11" s="3" t="n">
         <v>28.6</v>
@@ -11152,7 +11152,7 @@
         <v>27.2</v>
       </c>
       <c r="IR11" s="3" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="IS11" s="3" t="n">
         <v>3.7</v>
@@ -11366,7 +11366,7 @@
         <v>61</v>
       </c>
       <c r="AK12" s="6" t="n">
-        <v>54</v>
+        <v>54.1</v>
       </c>
       <c r="AL12" s="7" t="n">
         <v>49.7</v>
@@ -11381,19 +11381,19 @@
         <v>42</v>
       </c>
       <c r="AP12" s="7" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="AQ12" s="7" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="AR12" s="8" t="n">
         <v>37.4</v>
       </c>
       <c r="AS12" s="8" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="AT12" s="8" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="AU12" s="8" t="n">
         <v>30.9</v>
@@ -11405,13 +11405,13 @@
         <v>29.9</v>
       </c>
       <c r="AX12" s="8" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="AY12" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="AZ12" s="3" t="n">
-        <v>260.82</v>
+        <v>260.83</v>
       </c>
       <c r="BA12" s="4" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>60</v>
       </c>
       <c r="ID12" s="3" t="n">
-        <v>54</v>
+        <v>54.1</v>
       </c>
       <c r="IE12" s="3" t="n">
         <v>49.7</v>
@@ -12034,19 +12034,19 @@
         <v>42</v>
       </c>
       <c r="II12" s="3" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="IJ12" s="3" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="IK12" s="3" t="n">
         <v>37.4</v>
       </c>
       <c r="IL12" s="3" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="IM12" s="3" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="IN12" s="3" t="n">
         <v>30.9</v>
@@ -12058,7 +12058,7 @@
         <v>29.9</v>
       </c>
       <c r="IQ12" s="3" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="IR12" s="3" t="n">
         <v>23.6</v>
@@ -12266,40 +12266,40 @@
         <v>73.5</v>
       </c>
       <c r="AH13" s="5" t="n">
-        <v>68.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AI13" s="5" t="n">
-        <v>68.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="AJ13" s="5" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="AL13" s="6" t="n">
         <v>52.5</v>
       </c>
       <c r="AM13" s="7" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="AN13" s="7" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="AO13" s="7" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="AP13" s="8" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="AQ13" s="8" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="AR13" s="8" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="AS13" s="8" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="AT13" s="8" t="n">
         <v>31</v>
@@ -12314,13 +12314,13 @@
         <v>24.3</v>
       </c>
       <c r="AX13" s="8" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AY13" s="8" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AZ13" s="3" t="n">
-        <v>256.52</v>
+        <v>256.54</v>
       </c>
       <c r="BA13" s="4" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="BB13" s="9" t="inlineStr">
         <is>
-          <t>MORE 8.5 | 58.4% | Edge +2.3</t>
+          <t>MORE 8.5 | 58.5% | Edge +2.3</t>
         </is>
       </c>
       <c r="BC13" s="4" t="inlineStr">
@@ -12341,13 +12341,13 @@
         <v>8.5</v>
       </c>
       <c r="BE13" s="3" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="BF13" s="3" t="n">
         <v>2.26</v>
       </c>
       <c r="BG13" s="3" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="BH13" s="4" t="inlineStr">
         <is>
@@ -12919,40 +12919,40 @@
         <v>70</v>
       </c>
       <c r="IA13" s="3" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="IB13" s="3" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="IC13" s="3" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="ID13" s="3" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="IE13" s="3" t="n">
         <v>52.5</v>
       </c>
       <c r="IF13" s="3" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="IG13" s="3" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="IH13" s="3" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="II13" s="3" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="IJ13" s="3" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="IK13" s="3" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="IL13" s="3" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="IM13" s="3" t="n">
         <v>31</v>
@@ -12967,10 +12967,10 @@
         <v>24.3</v>
       </c>
       <c r="IQ13" s="3" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="IR13" s="3" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="IS13" s="3" t="n">
         <v>2.7</v>
@@ -13100,13 +13100,13 @@
         <v>10.93</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>10.68</v>
+        <v>10.67</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>10.68</v>
+        <v>10.67</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>8.539999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>8.73</v>
@@ -13115,13 +13115,13 @@
         <v>7.82</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>7.82</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.8</v>
+        <v>0.802</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>3.8</v>
@@ -13190,19 +13190,19 @@
         <v>47.9</v>
       </c>
       <c r="AM14" s="7" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="AN14" s="7" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="AO14" s="7" t="n">
         <v>41.1</v>
       </c>
       <c r="AP14" s="8" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="AQ14" s="8" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="AR14" s="8" t="n">
         <v>37</v>
@@ -13211,7 +13211,7 @@
         <v>37</v>
       </c>
       <c r="AT14" s="8" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="AU14" s="8" t="n">
         <v>30.6</v>
@@ -13229,7 +13229,7 @@
         <v>25.3</v>
       </c>
       <c r="AZ14" s="3" t="n">
-        <v>252.46</v>
+        <v>252.32</v>
       </c>
       <c r="BA14" s="4" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>59.6</v>
       </c>
       <c r="BF14" s="3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BG14" s="3" t="n">
         <v>19.2</v>
@@ -13776,13 +13776,13 @@
         <v>7.82</v>
       </c>
       <c r="HK14" s="3" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="HL14" s="3" t="n">
         <v>15.74</v>
       </c>
       <c r="HM14" s="3" t="n">
-        <v>21.34</v>
+        <v>21.35</v>
       </c>
       <c r="HN14" s="3" t="n">
         <v>4.52</v>
@@ -13843,19 +13843,19 @@
         <v>47.9</v>
       </c>
       <c r="IF14" s="3" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="IG14" s="3" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="IH14" s="3" t="n">
         <v>41.1</v>
       </c>
       <c r="II14" s="3" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="IJ14" s="3" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="IK14" s="3" t="n">
         <v>37</v>
@@ -13864,7 +13864,7 @@
         <v>37</v>
       </c>
       <c r="IM14" s="3" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="IN14" s="3" t="n">
         <v>30.6</v>
@@ -14009,10 +14009,10 @@
         <v>9.710000000000001</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>10.57</v>
+        <v>10.56</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>10.57</v>
+        <v>10.56</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>9.34</v>
@@ -14024,13 +14024,13 @@
         <v>6.14</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>7.85</v>
+        <v>7.84</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>6.14</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>6.8</v>
@@ -14066,10 +14066,10 @@
         <v>95.8</v>
       </c>
       <c r="AB15" s="5" t="n">
-        <v>92</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>91.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="AD15" s="5" t="n">
         <v>86.8</v>
@@ -14108,19 +14108,19 @@
         <v>41.2</v>
       </c>
       <c r="AP15" s="8" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="AQ15" s="8" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="AR15" s="8" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="AS15" s="8" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="AT15" s="8" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="AU15" s="8" t="n">
         <v>25.3</v>
@@ -14129,16 +14129,16 @@
         <v>25.3</v>
       </c>
       <c r="AW15" s="8" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AX15" s="8" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AY15" s="8" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AZ15" s="3" t="n">
-        <v>252.25</v>
+        <v>252.11</v>
       </c>
       <c r="BA15" s="4" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>58.3</v>
       </c>
       <c r="BF15" s="3" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="BG15" s="3" t="n">
         <v>16.6</v>
@@ -14691,7 +14691,7 @@
         <v>14.04</v>
       </c>
       <c r="HM15" s="3" t="n">
-        <v>18.73</v>
+        <v>18.74</v>
       </c>
       <c r="HN15" s="3" t="n">
         <v>4.62</v>
@@ -14719,10 +14719,10 @@
         <v>93.2</v>
       </c>
       <c r="HU15" s="3" t="n">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="HV15" s="3" t="n">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="HW15" s="3" t="n">
         <v>82.40000000000001</v>
@@ -14761,19 +14761,19 @@
         <v>41.2</v>
       </c>
       <c r="II15" s="3" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="IJ15" s="3" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="IK15" s="3" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="IL15" s="3" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="IM15" s="3" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="IN15" s="3" t="n">
         <v>25.3</v>
@@ -14782,13 +14782,13 @@
         <v>25.3</v>
       </c>
       <c r="IP15" s="3" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="IQ15" s="3" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="IR15" s="3" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="IS15" s="3" t="n">
         <v>2.7</v>
@@ -15795,168 +15795,168 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>ARI @ WSH</t>
+          <t>CIN @ STL</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>11.03</v>
+        <v>11.11</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>10.37</v>
+        <v>9.84</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>10.37</v>
+        <v>9.84</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>8.66</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>6.47</v>
+        <v>6.29</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>6.3</v>
+        <v>6.18</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>8.81</v>
+        <v>8.18</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>6.34</v>
+        <v>6.18</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>0.72</v>
+        <v>0.755</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>10.2</v>
+        <v>8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>5.73</v>
+        <v>9.27</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>10|6|16|7|12</t>
+          <t>12|0|3|14|11</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>10|6|16|7|12|3|0|0|5|0</t>
+          <t>12|0|3|14|11|5|5|14|5|5</t>
         </is>
       </c>
       <c r="X17" s="4" t="inlineStr">
         <is>
-          <t>10|6|16|7|12|3|0|0|5|0|3|7|10|5|2</t>
+          <t>12|0|3|14|11|5|5|14|5|5|18|19|8|16|4</t>
         </is>
       </c>
       <c r="Y17" s="5" t="n">
-        <v>99.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="Z17" s="5" t="n">
-        <v>92.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AA17" s="5" t="n">
-        <v>92.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AB17" s="5" t="n">
-        <v>91.7</v>
+        <v>89.2</v>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>88</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AD17" s="5" t="n">
-        <v>87.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AE17" s="5" t="n">
-        <v>78.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AF17" s="5" t="n">
-        <v>75.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AG17" s="5" t="n">
-        <v>75.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="AH17" s="5" t="n">
-        <v>64.7</v>
+        <v>61.1</v>
       </c>
       <c r="AI17" s="5" t="n">
-        <v>61.6</v>
+        <v>60.6</v>
       </c>
       <c r="AJ17" s="6" t="n">
-        <v>53.8</v>
+        <v>51.5</v>
       </c>
       <c r="AK17" s="7" t="n">
-        <v>52.8</v>
+        <v>46.1</v>
       </c>
       <c r="AL17" s="7" t="n">
-        <v>47.8</v>
+        <v>46.1</v>
       </c>
       <c r="AM17" s="7" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="AN17" s="7" t="n">
-        <v>44.6</v>
+        <v>41.5</v>
+      </c>
+      <c r="AN17" s="8" t="n">
+        <v>36.7</v>
       </c>
       <c r="AO17" s="8" t="n">
-        <v>39.6</v>
+        <v>36.7</v>
       </c>
       <c r="AP17" s="8" t="n">
-        <v>37.5</v>
+        <v>34</v>
       </c>
       <c r="AQ17" s="8" t="n">
-        <v>37.5</v>
+        <v>30.4</v>
       </c>
       <c r="AR17" s="8" t="n">
-        <v>34.2</v>
+        <v>30.4</v>
       </c>
       <c r="AS17" s="8" t="n">
-        <v>32.1</v>
+        <v>28.4</v>
       </c>
       <c r="AT17" s="8" t="n">
-        <v>27.4</v>
+        <v>24.5</v>
       </c>
       <c r="AU17" s="8" t="n">
-        <v>27.4</v>
+        <v>24.5</v>
       </c>
       <c r="AV17" s="8" t="n">
-        <v>25.8</v>
+        <v>22.8</v>
       </c>
       <c r="AW17" s="8" t="n">
-        <v>22.6</v>
+        <v>19.7</v>
       </c>
       <c r="AX17" s="8" t="n">
-        <v>22.6</v>
+        <v>19.7</v>
       </c>
       <c r="AY17" s="8" t="n">
-        <v>19.8</v>
+        <v>17.9</v>
       </c>
       <c r="AZ17" s="3" t="n">
-        <v>249.91</v>
+        <v>250.17</v>
       </c>
       <c r="BA17" s="4" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
       </c>
       <c r="BB17" s="9" t="inlineStr">
         <is>
-          <t>MORE 7.5 | 61.6% | Edge +2.9</t>
+          <t>MORE 7.5 | 60.6% | Edge +2.3</t>
         </is>
       </c>
       <c r="BC17" s="4" t="inlineStr">
@@ -15977,13 +15977,13 @@
         <v>7.5</v>
       </c>
       <c r="BE17" s="3" t="n">
-        <v>61.6</v>
+        <v>60.6</v>
       </c>
       <c r="BF17" s="3" t="n">
-        <v>2.87</v>
+        <v>2.34</v>
       </c>
       <c r="BG17" s="3" t="n">
-        <v>23.2</v>
+        <v>21.2</v>
       </c>
       <c r="BH17" s="4" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         </is>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ17" s="4" t="inlineStr">
         <is>
@@ -16000,24 +16000,24 @@
       </c>
       <c r="BK17" s="4" t="n"/>
       <c r="BL17" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BM17" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN17" s="4" t="inlineStr">
         <is>
-          <t>1-1-1-1-1-1</t>
+          <t>2-3-4-4-3-4-4</t>
         </is>
       </c>
       <c r="BO17" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="BP17" s="3" t="n">
         <v>97</v>
       </c>
       <c r="BQ17" s="3" t="n">
-        <v>5.13</v>
+        <v>4.82</v>
       </c>
       <c r="BR17" s="4" t="inlineStr">
         <is>
@@ -16032,133 +16032,133 @@
       </c>
       <c r="BU17" s="4" t="inlineStr">
         <is>
-          <t>Carson Palmquist</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="BV17" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="BW17" s="3" t="n">
-        <v>8.74</v>
+        <v>5.75</v>
       </c>
       <c r="BX17" s="3" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BY17" s="3" t="n">
-        <v>0.2963</v>
+        <v>0.2478</v>
       </c>
       <c r="BZ17" s="3" t="n">
-        <v>0.0185</v>
+        <v>0.0269</v>
       </c>
       <c r="CA17" s="3" t="n">
-        <v>0.0556</v>
+        <v>0.1045</v>
       </c>
       <c r="CB17" s="3" t="n">
-        <v>4.79</v>
+        <v>4.56</v>
       </c>
       <c r="CC17" s="3" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="CD17" s="3" t="n">
-        <v>0.2302</v>
+        <v>0.2142</v>
       </c>
       <c r="CE17" s="3" t="n">
-        <v>0.0356</v>
+        <v>0.0344</v>
       </c>
       <c r="CF17" s="4" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="CG17" s="3" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="CH17" s="3" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="CI17" s="3" t="n">
-        <v>81.8</v>
+        <v>77.5</v>
       </c>
       <c r="CJ17" s="3" t="n">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="CK17" s="3" t="n">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="CL17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM17" s="4" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="CN17" s="3" t="n">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="CO17" s="3" t="n">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="CP17" s="3" t="n">
-        <v>0.258</v>
+        <v>0.291</v>
       </c>
       <c r="CQ17" s="3" t="n">
-        <v>0.313</v>
+        <v>0.352</v>
       </c>
       <c r="CR17" s="3" t="n">
-        <v>0.461</v>
+        <v>0.519</v>
       </c>
       <c r="CS17" s="3" t="n">
-        <v>0.774</v>
+        <v>0.871</v>
       </c>
       <c r="CT17" s="3" t="n">
-        <v>115</v>
+        <v>315</v>
       </c>
       <c r="CU17" s="3" t="n">
-        <v>0.958</v>
+        <v>0.844</v>
       </c>
       <c r="CV17" s="3" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="CW17" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="CX17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="CZ17" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA17" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB17" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC17" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="CY17" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="CZ17" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="DA17" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="DB17" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="DC17" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="DD17" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="DE17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 vs Athletics: 10 FS|2026-07-21 vs Athletics: 6 FS|2026-07-20 vs Athletics: 16 FS|2026-07-19 vs St. Louis Cardinals: 7 FS|2026-07-18 vs St. Louis Cardinals: 12 FS</t>
+          <t>2026-07-23 vs Arizona Diamondbacks: 12 FS|2026-07-22 @ Los Angeles Angels: 0 FS|2026-07-21 @ Los Angeles Angels: 3 FS|2026-07-20 @ Los Angeles Angels: 14 FS|2026-07-19 @ Arizona Diamondbacks: 11 FS</t>
         </is>
       </c>
       <c r="DF17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 vs Athletics: 10 FS|2026-07-21 vs Athletics: 6 FS|2026-07-20 vs Athletics: 16 FS|2026-07-19 vs St. Louis Cardinals: 7 FS|2026-07-18 vs St. Louis Cardinals: 12 FS|2026-07-17 vs St. Louis Cardinals: 3 FS|2026-07-12 @ Los Angeles Dodgers: 0 FS|2026-07-11 @ Los Angeles Dodgers: 0 FS|2026-07-10 @ Los Angeles Dodgers: 5 FS|2026-07-09 @ San Diego Padres: 0 FS</t>
+          <t>2026-07-23 vs Arizona Diamondbacks: 12 FS|2026-07-22 @ Los Angeles Angels: 0 FS|2026-07-21 @ Los Angeles Angels: 3 FS|2026-07-20 @ Los Angeles Angels: 14 FS|2026-07-19 @ Arizona Diamondbacks: 11 FS|2026-07-18 @ Arizona Diamondbacks: 5 FS|2026-07-17 @ Arizona Diamondbacks: 5 FS|2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS</t>
         </is>
       </c>
       <c r="DG17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 vs Athletics: 10 FS|2026-07-21 vs Athletics: 6 FS|2026-07-20 vs Athletics: 16 FS|2026-07-19 vs St. Louis Cardinals: 7 FS|2026-07-18 vs St. Louis Cardinals: 12 FS|2026-07-17 vs St. Louis Cardinals: 3 FS|2026-07-12 @ Los Angeles Dodgers: 0 FS|2026-07-11 @ Los Angeles Dodgers: 0 FS|2026-07-10 @ Los Angeles Dodgers: 5 FS|2026-07-09 @ San Diego Padres: 0 FS|2026-07-08 @ San Diego Padres: 3 FS|2026-07-07 @ San Diego Padres: 7 FS|2026-07-06 @ San Diego Padres: 10 FS|2026-07-05 vs Milwaukee Brewers: 5 FS|2026-07-04 vs Milwaukee Brewers: 2 FS</t>
+          <t>2026-07-23 vs Arizona Diamondbacks: 12 FS|2026-07-22 @ Los Angeles Angels: 0 FS|2026-07-21 @ Los Angeles Angels: 3 FS|2026-07-20 @ Los Angeles Angels: 14 FS|2026-07-19 @ Arizona Diamondbacks: 11 FS|2026-07-18 @ Arizona Diamondbacks: 5 FS|2026-07-17 @ Arizona Diamondbacks: 5 FS|2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS|2026-07-09 vs Milwaukee Brewers: 18 FS|2026-07-08 vs Milwaukee Brewers: 19 FS|2026-07-07 vs Milwaukee Brewers: 8 FS|2026-07-07 vs Milwaukee Brewers: 16 FS|2026-07-06 vs Milwaukee Brewers: 4 FS</t>
         </is>
       </c>
       <c r="DH17" s="3" t="n">
@@ -16168,10 +16168,10 @@
         <v>30</v>
       </c>
       <c r="DJ17" s="3" t="n">
-        <v>9.130000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="DK17" s="3" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="DL17" s="4" t="inlineStr">
         <is>
@@ -16179,13 +16179,13 @@
         </is>
       </c>
       <c r="DM17" s="3" t="n">
-        <v>7.71</v>
+        <v>7.14</v>
       </c>
       <c r="DN17" s="3" t="n">
-        <v>6</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DO17" s="3" t="n">
-        <v>0.207</v>
+        <v>0.296</v>
       </c>
       <c r="DP17" s="4" t="inlineStr">
         <is>
@@ -16193,40 +16193,40 @@
         </is>
       </c>
       <c r="DQ17" s="3" t="n">
-        <v>9.130000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="DR17" s="3" t="n">
-        <v>1.333</v>
+        <v>2.328</v>
       </c>
       <c r="DS17" s="3" t="n">
-        <v>0.1905</v>
+        <v>0.2759</v>
       </c>
       <c r="DT17" s="3" t="n">
-        <v>0.0635</v>
+        <v>0.1034</v>
       </c>
       <c r="DU17" s="3" t="n">
-        <v>0.0159</v>
+        <v>0.0345</v>
       </c>
       <c r="DV17" s="3" t="n">
-        <v>0.0635</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="DW17" s="3" t="n">
-        <v>0</v>
+        <v>0.0517</v>
       </c>
       <c r="DX17" s="3" t="n">
-        <v>10.47</v>
+        <v>11.79</v>
       </c>
       <c r="DY17" s="3" t="n">
-        <v>10.94</v>
+        <v>11.02</v>
       </c>
       <c r="DZ17" s="3" t="n">
-        <v>9.09</v>
+        <v>10.99</v>
       </c>
       <c r="EA17" s="3" t="n">
-        <v>10.04</v>
+        <v>9.67</v>
       </c>
       <c r="EB17" s="3" t="n">
-        <v>10.44</v>
+        <v>10.01</v>
       </c>
       <c r="EC17" s="3" t="n">
         <v>28</v>
@@ -16249,13 +16249,13 @@
         </is>
       </c>
       <c r="EI17" s="3" t="n">
-        <v>8</v>
+        <v>16.34</v>
       </c>
       <c r="EJ17" s="3" t="n">
-        <v>25</v>
+        <v>48.1</v>
       </c>
       <c r="EK17" s="3" t="n">
-        <v>75</v>
+        <v>51.9</v>
       </c>
       <c r="EL17" s="4" t="inlineStr">
         <is>
@@ -16264,29 +16264,29 @@
       </c>
       <c r="EM17" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="EN17" s="3" t="n">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="EO17" s="3" t="n">
-        <v>38.4</v>
+        <v>37.9</v>
       </c>
       <c r="EP17" s="3" t="n">
-        <v>40.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="EQ17" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="ER17" s="3" t="n">
-        <v>1.0442</v>
+        <v>1.0558</v>
       </c>
       <c r="ES17" s="3" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="ET17" s="3" t="n">
-        <v>6.92</v>
+        <v>0.33</v>
       </c>
       <c r="EU17" s="3" t="n">
         <v>1</v>
@@ -16301,25 +16301,25 @@
         <v>75</v>
       </c>
       <c r="EY17" s="3" t="n">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="EZ17" s="3" t="n">
-        <v>85.7</v>
+        <v>85.81</v>
       </c>
       <c r="FA17" s="3" t="n">
-        <v>33.78</v>
+        <v>29.55</v>
       </c>
       <c r="FB17" s="3" t="n">
-        <v>1.69</v>
+        <v>2.02</v>
       </c>
       <c r="FC17" s="3" t="n">
-        <v>27.03</v>
+        <v>28.74</v>
       </c>
       <c r="FD17" s="3" t="n">
-        <v>0.382</v>
+        <v>0.433</v>
       </c>
       <c r="FE17" s="3" t="n">
-        <v>0.9736</v>
+        <v>1.0029</v>
       </c>
       <c r="FF17" s="3" t="n">
         <v>1</v>
@@ -16331,10 +16331,10 @@
         <v>1</v>
       </c>
       <c r="FI17" s="3" t="n">
-        <v>1.0299</v>
+        <v>0.9863</v>
       </c>
       <c r="FJ17" s="3" t="n">
-        <v>439</v>
+        <v>538</v>
       </c>
       <c r="FK17" s="4" t="inlineStr">
         <is>
@@ -16342,63 +16342,63 @@
         </is>
       </c>
       <c r="FL17" s="3" t="n">
-        <v>1</v>
+        <v>1.0603</v>
       </c>
       <c r="FM17" s="3" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="FN17" s="4" t="inlineStr">
         <is>
-          <t>Fallback</t>
+          <t>Statcast</t>
         </is>
       </c>
       <c r="FO17" s="3" t="n">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="FP17" s="3" t="n">
-        <v>85.7</v>
+        <v>85.81</v>
       </c>
       <c r="FQ17" s="3" t="n">
         <v>12</v>
       </c>
       <c r="FR17" s="3" t="n">
-        <v>14.81</v>
+        <v>10.98</v>
       </c>
       <c r="FS17" s="3" t="n">
-        <v>33.79</v>
+        <v>33.7</v>
       </c>
       <c r="FT17" s="3" t="n">
-        <v>16.9</v>
+        <v>21.9</v>
       </c>
       <c r="FU17" s="3" t="n">
-        <v>59.1</v>
+        <v>63.6</v>
       </c>
       <c r="FV17" s="3" t="n">
-        <v>24</v>
+        <v>14.6</v>
       </c>
       <c r="FW17" s="3" t="n">
-        <v>1.0137</v>
+        <v>0.9946</v>
       </c>
       <c r="FX17" s="3" t="n">
-        <v>1.0048</v>
+        <v>1.0035</v>
       </c>
       <c r="FY17" s="3" t="n">
-        <v>1.0317</v>
+        <v>1.0074</v>
       </c>
       <c r="FZ17" s="3" t="n">
-        <v>1.0097</v>
+        <v>1.007</v>
       </c>
       <c r="GA17" s="3" t="n">
-        <v>1.0464</v>
+        <v>1.0178</v>
       </c>
       <c r="GB17" s="3" t="n">
-        <v>0.985</v>
+        <v>1.0005</v>
       </c>
       <c r="GC17" s="3" t="n">
-        <v>7.88</v>
+        <v>8.81</v>
       </c>
       <c r="GD17" s="3" t="n">
-        <v>-1.25</v>
+        <v>0.05</v>
       </c>
       <c r="GE17" s="4" t="inlineStr">
         <is>
@@ -16443,52 +16443,52 @@
         <v>27</v>
       </c>
       <c r="GQ17" s="3" t="n">
-        <v>0.9281</v>
+        <v>1.3</v>
       </c>
       <c r="GR17" s="3" t="n">
         <v>27</v>
       </c>
       <c r="GS17" s="3" t="n">
-        <v>0.9989</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="GT17" s="3" t="n">
-        <v>0.1656</v>
+        <v>0.1888</v>
       </c>
       <c r="GU17" s="3" t="n">
-        <v>0.0566</v>
+        <v>0.0631</v>
       </c>
       <c r="GV17" s="3" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0002</v>
       </c>
       <c r="GW17" s="3" t="n">
-        <v>0.0595</v>
+        <v>0.0494</v>
       </c>
       <c r="GX17" s="3" t="n">
-        <v>0.0634</v>
+        <v>0.1078</v>
       </c>
       <c r="GY17" s="3" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0112</v>
       </c>
       <c r="GZ17" s="3" t="n">
-        <v>0.1724</v>
+        <v>0.2267</v>
       </c>
       <c r="HA17" s="3" t="n">
-        <v>0.4224</v>
+        <v>0.5</v>
       </c>
       <c r="HB17" s="3" t="n">
-        <v>0.3602</v>
+        <v>0.197</v>
       </c>
       <c r="HC17" s="3" t="n">
-        <v>0.2174</v>
+        <v>0.303</v>
       </c>
       <c r="HD17" s="3" t="n">
-        <v>0.101</v>
+        <v>0.067</v>
       </c>
       <c r="HE17" s="3" t="n">
-        <v>0.1535</v>
+        <v>0.2338</v>
       </c>
       <c r="HF17" s="3" t="n">
-        <v>0.0108</v>
+        <v>0.0181</v>
       </c>
       <c r="HG17" s="3" t="n">
         <v>1</v>
@@ -16500,19 +16500,19 @@
       </c>
       <c r="HI17" s="4" t="n"/>
       <c r="HJ17" s="3" t="n">
-        <v>6.34</v>
+        <v>6.18</v>
       </c>
       <c r="HK17" s="3" t="n">
-        <v>5.06</v>
+        <v>4.67</v>
       </c>
       <c r="HL17" s="3" t="n">
-        <v>14.42</v>
+        <v>12.98</v>
       </c>
       <c r="HM17" s="3" t="n">
-        <v>18.74</v>
+        <v>18.27</v>
       </c>
       <c r="HN17" s="3" t="n">
-        <v>4.65</v>
+        <v>4.37</v>
       </c>
       <c r="HO17" s="3" t="n">
         <v>0</v>
@@ -16528,103 +16528,103 @@
         </is>
       </c>
       <c r="HR17" s="3" t="n">
-        <v>100</v>
+        <v>89.8</v>
       </c>
       <c r="HS17" s="3" t="n">
-        <v>87.3</v>
+        <v>89.8</v>
       </c>
       <c r="HT17" s="3" t="n">
-        <v>87.3</v>
+        <v>89.8</v>
       </c>
       <c r="HU17" s="3" t="n">
-        <v>87.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="HV17" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="HW17" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="HX17" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="HY17" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="HZ17" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>61.7</v>
       </c>
       <c r="IA17" s="3" t="n">
-        <v>61.7</v>
+        <v>58.1</v>
       </c>
       <c r="IB17" s="3" t="n">
-        <v>59.1</v>
+        <v>58.1</v>
       </c>
       <c r="IC17" s="3" t="n">
-        <v>52.8</v>
+        <v>50.5</v>
       </c>
       <c r="ID17" s="3" t="n">
-        <v>52.8</v>
+        <v>46.1</v>
       </c>
       <c r="IE17" s="3" t="n">
-        <v>47.8</v>
+        <v>46.1</v>
       </c>
       <c r="IF17" s="3" t="n">
-        <v>44.6</v>
+        <v>41.5</v>
       </c>
       <c r="IG17" s="3" t="n">
-        <v>44.6</v>
+        <v>36.7</v>
       </c>
       <c r="IH17" s="3" t="n">
-        <v>39.6</v>
+        <v>36.7</v>
       </c>
       <c r="II17" s="3" t="n">
-        <v>37.5</v>
+        <v>34</v>
       </c>
       <c r="IJ17" s="3" t="n">
-        <v>37.5</v>
+        <v>30.4</v>
       </c>
       <c r="IK17" s="3" t="n">
-        <v>34.2</v>
+        <v>30.4</v>
       </c>
       <c r="IL17" s="3" t="n">
-        <v>32.1</v>
+        <v>28.4</v>
       </c>
       <c r="IM17" s="3" t="n">
-        <v>27.4</v>
+        <v>24.5</v>
       </c>
       <c r="IN17" s="3" t="n">
-        <v>27.4</v>
+        <v>24.5</v>
       </c>
       <c r="IO17" s="3" t="n">
-        <v>25.8</v>
+        <v>22.8</v>
       </c>
       <c r="IP17" s="3" t="n">
-        <v>22.6</v>
+        <v>19.7</v>
       </c>
       <c r="IQ17" s="3" t="n">
-        <v>22.6</v>
+        <v>19.7</v>
       </c>
       <c r="IR17" s="3" t="n">
-        <v>19.8</v>
+        <v>17.9</v>
       </c>
       <c r="IS17" s="3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="IT17" s="3" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="IU17" s="3" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="IV17" s="3" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="IW17" s="3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="IX17" s="3" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="IY17" s="3" t="n">
         <v>4.5</v>
@@ -16704,168 +16704,168 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>CIN @ STL</t>
+          <t>ARI @ WSH</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>11.11</v>
+        <v>11.03</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>9.82</v>
+        <v>10.37</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>9.82</v>
+        <v>10.37</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>8.44</v>
+        <v>8.66</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>6.29</v>
+        <v>6.47</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>6.18</v>
+        <v>6.3</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>8.17</v>
+        <v>8.81</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>6.18</v>
+        <v>6.34</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.757</v>
+        <v>0.72</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>8</v>
+        <v>10.2</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>9.27</v>
+        <v>5.73</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>12|0|3|14|11</t>
+          <t>10|6|16|7|12</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>12|0|3|14|11|5|5|14|5|5</t>
+          <t>10|6|16|7|12|3|0|0|5|0</t>
         </is>
       </c>
       <c r="X18" s="4" t="inlineStr">
         <is>
-          <t>12|0|3|14|11|5|5|14|5|5|18|19|8|16|4</t>
+          <t>10|6|16|7|12|3|0|0|5|0|3|7|10|5|2</t>
         </is>
       </c>
       <c r="Y18" s="5" t="n">
-        <v>93.90000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="Z18" s="5" t="n">
-        <v>93.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AA18" s="5" t="n">
-        <v>93.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AB18" s="5" t="n">
-        <v>89.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>88.3</v>
+        <v>88</v>
       </c>
       <c r="AD18" s="5" t="n">
-        <v>79.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="AE18" s="5" t="n">
-        <v>75.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AF18" s="5" t="n">
-        <v>75</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AG18" s="5" t="n">
-        <v>65.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AH18" s="5" t="n">
-        <v>61.1</v>
+        <v>64.7</v>
       </c>
       <c r="AI18" s="5" t="n">
-        <v>60.6</v>
+        <v>61.6</v>
       </c>
       <c r="AJ18" s="6" t="n">
-        <v>51.4</v>
+        <v>53.8</v>
       </c>
       <c r="AK18" s="7" t="n">
-        <v>46</v>
+        <v>52.8</v>
       </c>
       <c r="AL18" s="7" t="n">
-        <v>46</v>
+        <v>47.8</v>
       </c>
       <c r="AM18" s="7" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="AN18" s="8" t="n">
-        <v>36.6</v>
+        <v>44.6</v>
+      </c>
+      <c r="AN18" s="7" t="n">
+        <v>44.6</v>
       </c>
       <c r="AO18" s="8" t="n">
-        <v>36.6</v>
+        <v>39.6</v>
       </c>
       <c r="AP18" s="8" t="n">
-        <v>34</v>
+        <v>37.5</v>
       </c>
       <c r="AQ18" s="8" t="n">
-        <v>30.3</v>
+        <v>37.5</v>
       </c>
       <c r="AR18" s="8" t="n">
-        <v>30.3</v>
+        <v>34.2</v>
       </c>
       <c r="AS18" s="8" t="n">
-        <v>28.3</v>
+        <v>32.1</v>
       </c>
       <c r="AT18" s="8" t="n">
-        <v>24.4</v>
+        <v>27.4</v>
       </c>
       <c r="AU18" s="8" t="n">
-        <v>24.4</v>
+        <v>27.4</v>
       </c>
       <c r="AV18" s="8" t="n">
-        <v>22.7</v>
+        <v>25.8</v>
       </c>
       <c r="AW18" s="8" t="n">
-        <v>19.6</v>
+        <v>22.6</v>
       </c>
       <c r="AX18" s="8" t="n">
-        <v>19.6</v>
+        <v>22.6</v>
       </c>
       <c r="AY18" s="8" t="n">
-        <v>17.8</v>
+        <v>19.8</v>
       </c>
       <c r="AZ18" s="3" t="n">
-        <v>249.88</v>
+        <v>249.91</v>
       </c>
       <c r="BA18" s="4" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="BB18" s="9" t="inlineStr">
         <is>
-          <t>MORE 7.5 | 60.6% | Edge +2.3</t>
+          <t>MORE 7.5 | 61.6% | Edge +2.9</t>
         </is>
       </c>
       <c r="BC18" s="4" t="inlineStr">
@@ -16886,13 +16886,13 @@
         <v>7.5</v>
       </c>
       <c r="BE18" s="3" t="n">
-        <v>60.6</v>
+        <v>61.6</v>
       </c>
       <c r="BF18" s="3" t="n">
-        <v>2.32</v>
+        <v>2.87</v>
       </c>
       <c r="BG18" s="3" t="n">
-        <v>21.2</v>
+        <v>23.2</v>
       </c>
       <c r="BH18" s="4" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         </is>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BJ18" s="4" t="inlineStr">
         <is>
@@ -16909,24 +16909,24 @@
       </c>
       <c r="BK18" s="4" t="n"/>
       <c r="BL18" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BM18" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BN18" s="4" t="inlineStr">
         <is>
-          <t>2-3-4-4-3-4-4</t>
+          <t>1-1-1-1-1-1</t>
         </is>
       </c>
       <c r="BO18" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="BP18" s="3" t="n">
         <v>97</v>
       </c>
       <c r="BQ18" s="3" t="n">
-        <v>4.82</v>
+        <v>5.13</v>
       </c>
       <c r="BR18" s="4" t="inlineStr">
         <is>
@@ -16941,133 +16941,133 @@
       </c>
       <c r="BU18" s="4" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Carson Palmquist</t>
         </is>
       </c>
       <c r="BV18" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="BW18" s="3" t="n">
-        <v>5.75</v>
+        <v>8.74</v>
       </c>
       <c r="BX18" s="3" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="BY18" s="3" t="n">
-        <v>0.2478</v>
+        <v>0.2963</v>
       </c>
       <c r="BZ18" s="3" t="n">
-        <v>0.0269</v>
+        <v>0.0185</v>
       </c>
       <c r="CA18" s="3" t="n">
-        <v>0.1045</v>
+        <v>0.0556</v>
       </c>
       <c r="CB18" s="3" t="n">
-        <v>4.56</v>
+        <v>4.79</v>
       </c>
       <c r="CC18" s="3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="CD18" s="3" t="n">
-        <v>0.2142</v>
+        <v>0.2302</v>
       </c>
       <c r="CE18" s="3" t="n">
-        <v>0.0344</v>
+        <v>0.0356</v>
       </c>
       <c r="CF18" s="4" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="CG18" s="3" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="CH18" s="3" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="CI18" s="3" t="n">
-        <v>77.5</v>
+        <v>81.8</v>
       </c>
       <c r="CJ18" s="3" t="n">
-        <v>5.1</v>
+        <v>7.7</v>
       </c>
       <c r="CK18" s="3" t="n">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="CL18" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM18" s="4" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="CN18" s="3" t="n">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="CO18" s="3" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="CP18" s="3" t="n">
-        <v>0.291</v>
+        <v>0.258</v>
       </c>
       <c r="CQ18" s="3" t="n">
-        <v>0.352</v>
+        <v>0.313</v>
       </c>
       <c r="CR18" s="3" t="n">
-        <v>0.519</v>
+        <v>0.461</v>
       </c>
       <c r="CS18" s="3" t="n">
-        <v>0.871</v>
+        <v>0.774</v>
       </c>
       <c r="CT18" s="3" t="n">
-        <v>315</v>
+        <v>115</v>
       </c>
       <c r="CU18" s="3" t="n">
-        <v>0.844</v>
+        <v>0.958</v>
       </c>
       <c r="CV18" s="3" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="CW18" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="CX18" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CY18" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="CZ18" s="3" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="DA18" s="3" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="DB18" s="3" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="DC18" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DD18" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="DE18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23 vs Arizona Diamondbacks: 12 FS|2026-07-22 @ Los Angeles Angels: 0 FS|2026-07-21 @ Los Angeles Angels: 3 FS|2026-07-20 @ Los Angeles Angels: 14 FS|2026-07-19 @ Arizona Diamondbacks: 11 FS</t>
+          <t>2026-07-22 vs Athletics: 10 FS|2026-07-21 vs Athletics: 6 FS|2026-07-20 vs Athletics: 16 FS|2026-07-19 vs St. Louis Cardinals: 7 FS|2026-07-18 vs St. Louis Cardinals: 12 FS</t>
         </is>
       </c>
       <c r="DF18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23 vs Arizona Diamondbacks: 12 FS|2026-07-22 @ Los Angeles Angels: 0 FS|2026-07-21 @ Los Angeles Angels: 3 FS|2026-07-20 @ Los Angeles Angels: 14 FS|2026-07-19 @ Arizona Diamondbacks: 11 FS|2026-07-18 @ Arizona Diamondbacks: 5 FS|2026-07-17 @ Arizona Diamondbacks: 5 FS|2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS</t>
+          <t>2026-07-22 vs Athletics: 10 FS|2026-07-21 vs Athletics: 6 FS|2026-07-20 vs Athletics: 16 FS|2026-07-19 vs St. Louis Cardinals: 7 FS|2026-07-18 vs St. Louis Cardinals: 12 FS|2026-07-17 vs St. Louis Cardinals: 3 FS|2026-07-12 @ Los Angeles Dodgers: 0 FS|2026-07-11 @ Los Angeles Dodgers: 0 FS|2026-07-10 @ Los Angeles Dodgers: 5 FS|2026-07-09 @ San Diego Padres: 0 FS</t>
         </is>
       </c>
       <c r="DG18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23 vs Arizona Diamondbacks: 12 FS|2026-07-22 @ Los Angeles Angels: 0 FS|2026-07-21 @ Los Angeles Angels: 3 FS|2026-07-20 @ Los Angeles Angels: 14 FS|2026-07-19 @ Arizona Diamondbacks: 11 FS|2026-07-18 @ Arizona Diamondbacks: 5 FS|2026-07-17 @ Arizona Diamondbacks: 5 FS|2026-07-12 vs Atlanta Braves: 14 FS|2026-07-11 vs Atlanta Braves: 5 FS|2026-07-10 vs Atlanta Braves: 5 FS|2026-07-09 vs Milwaukee Brewers: 18 FS|2026-07-08 vs Milwaukee Brewers: 19 FS|2026-07-07 vs Milwaukee Brewers: 8 FS|2026-07-07 vs Milwaukee Brewers: 16 FS|2026-07-06 vs Milwaukee Brewers: 4 FS</t>
+          <t>2026-07-22 vs Athletics: 10 FS|2026-07-21 vs Athletics: 6 FS|2026-07-20 vs Athletics: 16 FS|2026-07-19 vs St. Louis Cardinals: 7 FS|2026-07-18 vs St. Louis Cardinals: 12 FS|2026-07-17 vs St. Louis Cardinals: 3 FS|2026-07-12 @ Los Angeles Dodgers: 0 FS|2026-07-11 @ Los Angeles Dodgers: 0 FS|2026-07-10 @ Los Angeles Dodgers: 5 FS|2026-07-09 @ San Diego Padres: 0 FS|2026-07-08 @ San Diego Padres: 3 FS|2026-07-07 @ San Diego Padres: 7 FS|2026-07-06 @ San Diego Padres: 10 FS|2026-07-05 vs Milwaukee Brewers: 5 FS|2026-07-04 vs Milwaukee Brewers: 2 FS</t>
         </is>
       </c>
       <c r="DH18" s="3" t="n">
@@ -17077,10 +17077,10 @@
         <v>30</v>
       </c>
       <c r="DJ18" s="3" t="n">
-        <v>8.77</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DK18" s="3" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="DL18" s="4" t="inlineStr">
         <is>
@@ -17088,13 +17088,13 @@
         </is>
       </c>
       <c r="DM18" s="3" t="n">
-        <v>7.14</v>
+        <v>7.71</v>
       </c>
       <c r="DN18" s="3" t="n">
-        <v>9.640000000000001</v>
+        <v>6</v>
       </c>
       <c r="DO18" s="3" t="n">
-        <v>0.296</v>
+        <v>0.207</v>
       </c>
       <c r="DP18" s="4" t="inlineStr">
         <is>
@@ -17102,40 +17102,40 @@
         </is>
       </c>
       <c r="DQ18" s="3" t="n">
-        <v>8.77</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DR18" s="3" t="n">
-        <v>2.328</v>
+        <v>1.333</v>
       </c>
       <c r="DS18" s="3" t="n">
-        <v>0.2759</v>
+        <v>0.1905</v>
       </c>
       <c r="DT18" s="3" t="n">
-        <v>0.1034</v>
+        <v>0.0635</v>
       </c>
       <c r="DU18" s="3" t="n">
-        <v>0.0345</v>
+        <v>0.0159</v>
       </c>
       <c r="DV18" s="3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0635</v>
       </c>
       <c r="DW18" s="3" t="n">
-        <v>0.0517</v>
+        <v>0</v>
       </c>
       <c r="DX18" s="3" t="n">
-        <v>11.79</v>
+        <v>10.47</v>
       </c>
       <c r="DY18" s="3" t="n">
-        <v>11.02</v>
+        <v>10.94</v>
       </c>
       <c r="DZ18" s="3" t="n">
-        <v>10.99</v>
+        <v>9.09</v>
       </c>
       <c r="EA18" s="3" t="n">
-        <v>9.67</v>
+        <v>10.04</v>
       </c>
       <c r="EB18" s="3" t="n">
-        <v>10.01</v>
+        <v>10.44</v>
       </c>
       <c r="EC18" s="3" t="n">
         <v>28</v>
@@ -17158,13 +17158,13 @@
         </is>
       </c>
       <c r="EI18" s="3" t="n">
-        <v>16.34</v>
+        <v>8</v>
       </c>
       <c r="EJ18" s="3" t="n">
-        <v>48.1</v>
+        <v>25</v>
       </c>
       <c r="EK18" s="3" t="n">
-        <v>51.9</v>
+        <v>75</v>
       </c>
       <c r="EL18" s="4" t="inlineStr">
         <is>
@@ -17173,29 +17173,29 @@
       </c>
       <c r="EM18" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="EN18" s="3" t="n">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="EO18" s="3" t="n">
-        <v>37.9</v>
+        <v>38.4</v>
       </c>
       <c r="EP18" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>40.4</v>
       </c>
       <c r="EQ18" s="3" t="n">
-        <v>69.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="ER18" s="3" t="n">
-        <v>1.0558</v>
+        <v>1.0442</v>
       </c>
       <c r="ES18" s="3" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="ET18" s="3" t="n">
-        <v>0.33</v>
+        <v>6.92</v>
       </c>
       <c r="EU18" s="3" t="n">
         <v>1</v>
@@ -17210,25 +17210,25 @@
         <v>75</v>
       </c>
       <c r="EY18" s="3" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="EZ18" s="3" t="n">
-        <v>85.81</v>
+        <v>85.7</v>
       </c>
       <c r="FA18" s="3" t="n">
-        <v>29.55</v>
+        <v>33.78</v>
       </c>
       <c r="FB18" s="3" t="n">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="FC18" s="3" t="n">
-        <v>28.74</v>
+        <v>27.03</v>
       </c>
       <c r="FD18" s="3" t="n">
-        <v>0.433</v>
+        <v>0.382</v>
       </c>
       <c r="FE18" s="3" t="n">
-        <v>1.0029</v>
+        <v>0.9736</v>
       </c>
       <c r="FF18" s="3" t="n">
         <v>1</v>
@@ -17240,10 +17240,10 @@
         <v>1</v>
       </c>
       <c r="FI18" s="3" t="n">
-        <v>0.9863</v>
+        <v>1.0299</v>
       </c>
       <c r="FJ18" s="3" t="n">
-        <v>538</v>
+        <v>439</v>
       </c>
       <c r="FK18" s="4" t="inlineStr">
         <is>
@@ -17251,63 +17251,63 @@
         </is>
       </c>
       <c r="FL18" s="3" t="n">
-        <v>1.0603</v>
+        <v>1</v>
       </c>
       <c r="FM18" s="3" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="FN18" s="4" t="inlineStr">
         <is>
-          <t>Statcast</t>
+          <t>Fallback</t>
         </is>
       </c>
       <c r="FO18" s="3" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="FP18" s="3" t="n">
-        <v>85.81</v>
+        <v>85.7</v>
       </c>
       <c r="FQ18" s="3" t="n">
         <v>12</v>
       </c>
       <c r="FR18" s="3" t="n">
-        <v>10.98</v>
+        <v>14.81</v>
       </c>
       <c r="FS18" s="3" t="n">
-        <v>33.7</v>
+        <v>33.79</v>
       </c>
       <c r="FT18" s="3" t="n">
-        <v>21.9</v>
+        <v>16.9</v>
       </c>
       <c r="FU18" s="3" t="n">
-        <v>63.6</v>
+        <v>59.1</v>
       </c>
       <c r="FV18" s="3" t="n">
-        <v>14.6</v>
+        <v>24</v>
       </c>
       <c r="FW18" s="3" t="n">
-        <v>0.9946</v>
+        <v>1.0137</v>
       </c>
       <c r="FX18" s="3" t="n">
-        <v>1.0035</v>
+        <v>1.0048</v>
       </c>
       <c r="FY18" s="3" t="n">
-        <v>1.0074</v>
+        <v>1.0317</v>
       </c>
       <c r="FZ18" s="3" t="n">
-        <v>1.007</v>
+        <v>1.0097</v>
       </c>
       <c r="GA18" s="3" t="n">
-        <v>1.0178</v>
+        <v>1.0464</v>
       </c>
       <c r="GB18" s="3" t="n">
-        <v>1.0005</v>
+        <v>0.985</v>
       </c>
       <c r="GC18" s="3" t="n">
-        <v>8.81</v>
+        <v>7.88</v>
       </c>
       <c r="GD18" s="3" t="n">
-        <v>0.05</v>
+        <v>-1.25</v>
       </c>
       <c r="GE18" s="4" t="inlineStr">
         <is>
@@ -17352,52 +17352,52 @@
         <v>27</v>
       </c>
       <c r="GQ18" s="3" t="n">
-        <v>1.3</v>
+        <v>0.9281</v>
       </c>
       <c r="GR18" s="3" t="n">
         <v>27</v>
       </c>
       <c r="GS18" s="3" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9989</v>
       </c>
       <c r="GT18" s="3" t="n">
-        <v>0.1888</v>
+        <v>0.1656</v>
       </c>
       <c r="GU18" s="3" t="n">
-        <v>0.0631</v>
+        <v>0.0566</v>
       </c>
       <c r="GV18" s="3" t="n">
-        <v>0.0002</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="GW18" s="3" t="n">
-        <v>0.0494</v>
+        <v>0.0595</v>
       </c>
       <c r="GX18" s="3" t="n">
-        <v>0.1078</v>
+        <v>0.0634</v>
       </c>
       <c r="GY18" s="3" t="n">
-        <v>0.0112</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="GZ18" s="3" t="n">
-        <v>0.2267</v>
+        <v>0.1724</v>
       </c>
       <c r="HA18" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4224</v>
       </c>
       <c r="HB18" s="3" t="n">
-        <v>0.197</v>
+        <v>0.3602</v>
       </c>
       <c r="HC18" s="3" t="n">
-        <v>0.303</v>
+        <v>0.2174</v>
       </c>
       <c r="HD18" s="3" t="n">
-        <v>0.067</v>
+        <v>0.101</v>
       </c>
       <c r="HE18" s="3" t="n">
-        <v>0.2338</v>
+        <v>0.1535</v>
       </c>
       <c r="HF18" s="3" t="n">
-        <v>0.0181</v>
+        <v>0.0108</v>
       </c>
       <c r="HG18" s="3" t="n">
         <v>1</v>
@@ -17409,19 +17409,19 @@
       </c>
       <c r="HI18" s="4" t="n"/>
       <c r="HJ18" s="3" t="n">
-        <v>6.18</v>
+        <v>6.34</v>
       </c>
       <c r="HK18" s="3" t="n">
-        <v>4.66</v>
+        <v>5.06</v>
       </c>
       <c r="HL18" s="3" t="n">
-        <v>12.98</v>
+        <v>14.42</v>
       </c>
       <c r="HM18" s="3" t="n">
-        <v>18.28</v>
+        <v>18.74</v>
       </c>
       <c r="HN18" s="3" t="n">
-        <v>4.37</v>
+        <v>4.65</v>
       </c>
       <c r="HO18" s="3" t="n">
         <v>0</v>
@@ -17437,103 +17437,103 @@
         </is>
       </c>
       <c r="HR18" s="3" t="n">
-        <v>89.8</v>
+        <v>100</v>
       </c>
       <c r="HS18" s="3" t="n">
-        <v>89.8</v>
+        <v>87.3</v>
       </c>
       <c r="HT18" s="3" t="n">
-        <v>89.8</v>
+        <v>87.3</v>
       </c>
       <c r="HU18" s="3" t="n">
-        <v>83.3</v>
+        <v>87.3</v>
       </c>
       <c r="HV18" s="3" t="n">
-        <v>83.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="HW18" s="3" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="HX18" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="HX18" s="3" t="n">
-        <v>71</v>
-      </c>
       <c r="HY18" s="3" t="n">
-        <v>71</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="HZ18" s="3" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="IA18" s="3" t="n">
         <v>61.7</v>
       </c>
-      <c r="IA18" s="3" t="n">
-        <v>58.1</v>
-      </c>
       <c r="IB18" s="3" t="n">
-        <v>58.1</v>
+        <v>59.1</v>
       </c>
       <c r="IC18" s="3" t="n">
-        <v>50.4</v>
+        <v>52.8</v>
       </c>
       <c r="ID18" s="3" t="n">
-        <v>46</v>
+        <v>52.8</v>
       </c>
       <c r="IE18" s="3" t="n">
-        <v>46</v>
+        <v>47.8</v>
       </c>
       <c r="IF18" s="3" t="n">
-        <v>41.5</v>
+        <v>44.6</v>
       </c>
       <c r="IG18" s="3" t="n">
-        <v>36.6</v>
+        <v>44.6</v>
       </c>
       <c r="IH18" s="3" t="n">
-        <v>36.6</v>
+        <v>39.6</v>
       </c>
       <c r="II18" s="3" t="n">
-        <v>34</v>
+        <v>37.5</v>
       </c>
       <c r="IJ18" s="3" t="n">
-        <v>30.3</v>
+        <v>37.5</v>
       </c>
       <c r="IK18" s="3" t="n">
-        <v>30.3</v>
+        <v>34.2</v>
       </c>
       <c r="IL18" s="3" t="n">
-        <v>28.3</v>
+        <v>32.1</v>
       </c>
       <c r="IM18" s="3" t="n">
-        <v>24.4</v>
+        <v>27.4</v>
       </c>
       <c r="IN18" s="3" t="n">
-        <v>24.4</v>
+        <v>27.4</v>
       </c>
       <c r="IO18" s="3" t="n">
-        <v>22.7</v>
+        <v>25.8</v>
       </c>
       <c r="IP18" s="3" t="n">
-        <v>19.6</v>
+        <v>22.6</v>
       </c>
       <c r="IQ18" s="3" t="n">
-        <v>19.6</v>
+        <v>22.6</v>
       </c>
       <c r="IR18" s="3" t="n">
-        <v>17.8</v>
+        <v>19.8</v>
       </c>
       <c r="IS18" s="3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="IT18" s="3" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="IU18" s="3" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="IV18" s="3" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="IW18" s="3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="IX18" s="3" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="IY18" s="3" t="n">
         <v>4.5</v>
@@ -18554,13 +18554,13 @@
         <v>9.130000000000001</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10.6</v>
+        <v>10.61</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>10.6</v>
+        <v>10.61</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>8.58</v>
+        <v>8.59</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>7.47</v>
@@ -18569,13 +18569,13 @@
         <v>6.95</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>8.970000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>6.95</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>6.6</v>
@@ -18611,10 +18611,10 @@
         <v>93.3</v>
       </c>
       <c r="AB20" s="5" t="n">
-        <v>88.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>87.2</v>
+        <v>87.3</v>
       </c>
       <c r="AD20" s="5" t="n">
         <v>80.8</v>
@@ -18626,10 +18626,10 @@
         <v>75.3</v>
       </c>
       <c r="AG20" s="5" t="n">
-        <v>66.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AH20" s="5" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AI20" s="5" t="n">
         <v>62.4</v>
@@ -18644,46 +18644,46 @@
         <v>48.6</v>
       </c>
       <c r="AM20" s="7" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="AN20" s="7" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="AO20" s="8" t="n">
-        <v>39.9</v>
+        <v>43.6</v>
+      </c>
+      <c r="AO20" s="7" t="n">
+        <v>40</v>
       </c>
       <c r="AP20" s="8" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="AQ20" s="8" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="AR20" s="8" t="n">
         <v>34.3</v>
       </c>
       <c r="AS20" s="8" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="AT20" s="8" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="AU20" s="8" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="AV20" s="8" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="AW20" s="8" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="AX20" s="8" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AY20" s="8" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AZ20" s="3" t="n">
-        <v>244.28</v>
+        <v>244.43</v>
       </c>
       <c r="BA20" s="4" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>62.4</v>
       </c>
       <c r="BF20" s="3" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="BG20" s="3" t="n">
         <v>24.8</v>
@@ -19222,13 +19222,13 @@
         <v>6.95</v>
       </c>
       <c r="HK20" s="3" t="n">
-        <v>5.48</v>
+        <v>5.49</v>
       </c>
       <c r="HL20" s="3" t="n">
         <v>14.78</v>
       </c>
       <c r="HM20" s="3" t="n">
-        <v>20.21</v>
+        <v>20.2</v>
       </c>
       <c r="HN20" s="3" t="n">
         <v>4.36</v>
@@ -19256,10 +19256,10 @@
         <v>89.3</v>
       </c>
       <c r="HU20" s="3" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="HV20" s="3" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="HW20" s="3" t="n">
         <v>75.8</v>
@@ -19271,10 +19271,10 @@
         <v>71.3</v>
       </c>
       <c r="HZ20" s="3" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="IA20" s="3" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="IB20" s="3" t="n">
         <v>59.9</v>
@@ -19289,43 +19289,43 @@
         <v>48.6</v>
       </c>
       <c r="IF20" s="3" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="IG20" s="3" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="IH20" s="3" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="II20" s="3" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="IJ20" s="3" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="IK20" s="3" t="n">
         <v>34.3</v>
       </c>
       <c r="IL20" s="3" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="IM20" s="3" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="IN20" s="3" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="IO20" s="3" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="IP20" s="3" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="IQ20" s="3" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="IR20" s="3" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="IS20" s="3" t="n">
         <v>4.3</v>
@@ -19455,10 +19455,10 @@
         <v>10.32</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>9.93</v>
+        <v>9.94</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>9.93</v>
+        <v>9.94</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>7.5</v>
@@ -19470,13 +19470,13 @@
         <v>7.37</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>8.880000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>7.37</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.83</v>
+        <v>0.829</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>5.4</v>
@@ -19539,25 +19539,25 @@
         <v>47.4</v>
       </c>
       <c r="AK21" s="7" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="AL21" s="7" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="AM21" s="8" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="AN21" s="8" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="AO21" s="8" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="AP21" s="8" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="AQ21" s="8" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="AR21" s="8" t="n">
         <v>32</v>
@@ -19578,13 +19578,13 @@
         <v>26.2</v>
       </c>
       <c r="AX21" s="8" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AY21" s="8" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AZ21" s="3" t="n">
-        <v>243.75</v>
+        <v>243.88</v>
       </c>
       <c r="BA21" s="4" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>61.7</v>
       </c>
       <c r="BF21" s="3" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="BG21" s="3" t="n">
         <v>23.4</v>
@@ -20134,7 +20134,7 @@
         <v>4.18</v>
       </c>
       <c r="HL21" s="3" t="n">
-        <v>14.97</v>
+        <v>14.96</v>
       </c>
       <c r="HM21" s="3" t="n">
         <v>19.94</v>
@@ -20192,25 +20192,25 @@
         <v>46.4</v>
       </c>
       <c r="ID21" s="3" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="IE21" s="3" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="IF21" s="3" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="IG21" s="3" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="IH21" s="3" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="II21" s="3" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="IJ21" s="3" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="IK21" s="3" t="n">
         <v>32</v>
@@ -20231,10 +20231,10 @@
         <v>26.2</v>
       </c>
       <c r="IQ21" s="3" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="IR21" s="3" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="IS21" s="3" t="n">
         <v>4</v>
@@ -21271,7 +21271,7 @@
         <v>9.33</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>7.43</v>
+        <v>7.44</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>7.07</v>
@@ -21280,13 +21280,13 @@
         <v>6.69</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>8.220000000000001</v>
+        <v>8.23</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>6.69</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>12</v>
@@ -21325,7 +21325,7 @@
         <v>85.2</v>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>77.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="AD23" s="5" t="n">
         <v>72</v>
@@ -21334,28 +21334,28 @@
         <v>71.5</v>
       </c>
       <c r="AF23" s="5" t="n">
-        <v>61.6</v>
+        <v>61.7</v>
       </c>
       <c r="AG23" s="5" t="n">
-        <v>61.1</v>
+        <v>61.2</v>
       </c>
       <c r="AH23" s="6" t="n">
         <v>57.5</v>
       </c>
       <c r="AI23" s="7" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="AJ23" s="7" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="AK23" s="7" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="AL23" s="7" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="AM23" s="8" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="AN23" s="8" t="n">
         <v>34.6</v>
@@ -21382,10 +21382,10 @@
         <v>23.7</v>
       </c>
       <c r="AV23" s="8" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AW23" s="8" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AX23" s="8" t="n">
         <v>18.7</v>
@@ -21394,7 +21394,7 @@
         <v>18.7</v>
       </c>
       <c r="AZ23" s="3" t="n">
-        <v>241.16</v>
+        <v>241.19</v>
       </c>
       <c r="BA23" s="4" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="BB23" s="9" t="inlineStr">
         <is>
-          <t>MORE 6.5 | 61.1% | Edge +2.8</t>
+          <t>MORE 6.5 | 61.2% | Edge +2.8</t>
         </is>
       </c>
       <c r="BC23" s="4" t="inlineStr">
@@ -21415,13 +21415,13 @@
         <v>6.5</v>
       </c>
       <c r="BE23" s="3" t="n">
-        <v>61.1</v>
+        <v>61.2</v>
       </c>
       <c r="BF23" s="3" t="n">
         <v>2.83</v>
       </c>
       <c r="BG23" s="3" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="BH23" s="4" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>78.2</v>
       </c>
       <c r="HV23" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="HW23" s="3" t="n">
         <v>67</v>
@@ -21987,28 +21987,28 @@
         <v>67</v>
       </c>
       <c r="HY23" s="3" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="HZ23" s="3" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="IA23" s="3" t="n">
         <v>54.5</v>
       </c>
       <c r="IB23" s="3" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="IC23" s="3" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="ID23" s="3" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="IE23" s="3" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="IF23" s="3" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="IG23" s="3" t="n">
         <v>34.6</v>
@@ -22035,10 +22035,10 @@
         <v>23.7</v>
       </c>
       <c r="IO23" s="3" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="IP23" s="3" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="IQ23" s="3" t="n">
         <v>18.7</v>
@@ -24861,168 +24861,168 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Shea Langeliers</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>LAA @ SF</t>
+          <t>ATH @ MIN</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>LF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>9.48</v>
+        <v>9.42</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>9.57</v>
+        <v>9.68</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>9.57</v>
+        <v>9.68</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>8.17</v>
+        <v>7.75</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>7.51</v>
+        <v>5.59</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>6.98</v>
+        <v>5.75</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>7.85</v>
+        <v>8.91</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>6.98</v>
+        <v>6.41</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.889</v>
+        <v>0.72</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>5.2</v>
+        <v>10.4</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>7.93</v>
+        <v>7.73</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>0|4|14|5|3</t>
+          <t>6|16|7|8|15</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>0|4|14|5|3|8|6|5|0|5</t>
+          <t>6|16|7|8|15|14|14|0|0|7</t>
         </is>
       </c>
       <c r="X27" s="4" t="inlineStr">
         <is>
-          <t>0|4|14|5|3|8|6|5|0|5|3|10|44|5|7</t>
+          <t>6|16|7|8|15|14|14|0|0|7|0|7|0|17|5</t>
         </is>
       </c>
       <c r="Y27" s="5" t="n">
-        <v>92.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="Z27" s="5" t="n">
-        <v>90.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="AA27" s="5" t="n">
-        <v>90.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AB27" s="5" t="n">
-        <v>81.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>80.2</v>
+        <v>83.8</v>
       </c>
       <c r="AD27" s="5" t="n">
-        <v>77.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AE27" s="5" t="n">
-        <v>77.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AF27" s="5" t="n">
-        <v>65.7</v>
+        <v>69</v>
       </c>
       <c r="AG27" s="5" t="n">
-        <v>61.5</v>
+        <v>59.3</v>
       </c>
       <c r="AH27" s="5" t="n">
-        <v>61</v>
+        <v>58.8</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>54.3</v>
+        <v>55.2</v>
       </c>
       <c r="AJ27" s="7" t="n">
-        <v>52.8</v>
+        <v>47.4</v>
       </c>
       <c r="AK27" s="7" t="n">
-        <v>45.7</v>
+        <v>42.8</v>
       </c>
       <c r="AL27" s="7" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="AM27" s="7" t="n">
-        <v>42</v>
+        <v>42.8</v>
+      </c>
+      <c r="AM27" s="8" t="n">
+        <v>39.6</v>
       </c>
       <c r="AN27" s="8" t="n">
-        <v>35.8</v>
+        <v>36.6</v>
       </c>
       <c r="AO27" s="8" t="n">
-        <v>35.8</v>
+        <v>36.6</v>
       </c>
       <c r="AP27" s="8" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="AQ27" s="8" t="n">
-        <v>33.3</v>
+        <v>32.7</v>
       </c>
       <c r="AR27" s="8" t="n">
-        <v>29.2</v>
+        <v>32.7</v>
       </c>
       <c r="AS27" s="8" t="n">
-        <v>29.2</v>
+        <v>31.6</v>
       </c>
       <c r="AT27" s="8" t="n">
-        <v>26.5</v>
+        <v>26.9</v>
       </c>
       <c r="AU27" s="8" t="n">
-        <v>26.5</v>
+        <v>26.9</v>
       </c>
       <c r="AV27" s="8" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="AW27" s="8" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="AX27" s="8" t="n">
-        <v>20.7</v>
+        <v>20</v>
       </c>
       <c r="AY27" s="8" t="n">
-        <v>18.3</v>
+        <v>20</v>
       </c>
       <c r="AZ27" s="3" t="n">
-        <v>236.76</v>
+        <v>236.86</v>
       </c>
       <c r="BA27" s="4" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="BB27" s="9" t="inlineStr">
         <is>
-          <t>MORE 7.0 | 61.0% | Edge +2.6</t>
+          <t>MORE 7.0 | 58.8% | Edge +2.7</t>
         </is>
       </c>
       <c r="BC27" s="4" t="inlineStr">
@@ -25043,13 +25043,13 @@
         <v>7</v>
       </c>
       <c r="BE27" s="3" t="n">
-        <v>61</v>
+        <v>58.8</v>
       </c>
       <c r="BF27" s="3" t="n">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="BG27" s="3" t="n">
-        <v>22</v>
+        <v>17.6</v>
       </c>
       <c r="BH27" s="4" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         </is>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BJ27" s="4" t="inlineStr">
         <is>
@@ -25066,24 +25066,24 @@
       </c>
       <c r="BK27" s="4" t="n"/>
       <c r="BL27" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BM27" s="3" t="n">
         <v>7</v>
       </c>
       <c r="BN27" s="4" t="inlineStr">
         <is>
-          <t>3-1-5-5-5-5-1</t>
+          <t>3-3-3-3-3-4-3</t>
         </is>
       </c>
       <c r="BO27" s="3" t="n">
-        <v>57.1</v>
+        <v>85.7</v>
       </c>
       <c r="BP27" s="3" t="n">
         <v>97</v>
       </c>
       <c r="BQ27" s="3" t="n">
-        <v>4.52</v>
+        <v>4.92</v>
       </c>
       <c r="BR27" s="4" t="inlineStr">
         <is>
@@ -25091,14 +25091,14 @@
         </is>
       </c>
       <c r="BS27" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BT27" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="BU27" s="4" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Zebby Matthews</t>
         </is>
       </c>
       <c r="BV27" s="4" t="inlineStr">
@@ -25107,124 +25107,124 @@
         </is>
       </c>
       <c r="BW27" s="3" t="n">
-        <v>8.23</v>
+        <v>5.4</v>
       </c>
       <c r="BX27" s="3" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="BY27" s="3" t="n">
-        <v>0.2679</v>
+        <v>0.2458</v>
       </c>
       <c r="BZ27" s="3" t="n">
-        <v>0.0298</v>
+        <v>0.0505</v>
       </c>
       <c r="CA27" s="3" t="n">
-        <v>0.1012</v>
+        <v>0.0707</v>
       </c>
       <c r="CB27" s="3" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="CC27" s="3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="CD27" s="3" t="n">
-        <v>0.2038</v>
+        <v>0.2235</v>
       </c>
       <c r="CE27" s="3" t="n">
-        <v>0.0278</v>
+        <v>0.0313</v>
       </c>
       <c r="CF27" s="4" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="CG27" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="CH27" s="3" t="n">
-        <v>1.025</v>
+        <v>1</v>
       </c>
       <c r="CI27" s="3" t="n">
-        <v>68</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="CJ27" s="3" t="n">
-        <v>17.6</v>
+        <v>6.8</v>
       </c>
       <c r="CK27" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="CL27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM27" s="4" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="CN27" s="3" t="n">
+        <v>412</v>
+      </c>
+      <c r="CO27" s="3" t="n">
+        <v>372</v>
+      </c>
+      <c r="CP27" s="3" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="CQ27" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="CR27" s="3" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="CS27" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="CT27" s="3" t="n">
         <v>285</v>
       </c>
-      <c r="CL27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM27" s="4" t="inlineStr">
-        <is>
-          <t>windy</t>
-        </is>
-      </c>
-      <c r="CN27" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="CO27" s="3" t="n">
-        <v>246</v>
-      </c>
-      <c r="CP27" s="3" t="n">
-        <v>0.268</v>
-      </c>
-      <c r="CQ27" s="3" t="n">
-        <v>0.304</v>
-      </c>
-      <c r="CR27" s="3" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="CS27" s="3" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="CT27" s="3" t="n">
-        <v>203</v>
-      </c>
       <c r="CU27" s="3" t="n">
-        <v>0.718</v>
+        <v>0.747</v>
       </c>
       <c r="CV27" s="3" t="n">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="CW27" s="3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="CX27" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CY27" s="3" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="CZ27" s="3" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="DA27" s="3" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="DB27" s="3" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="DC27" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="DD27" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DE27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Kansas City Royals: 0 FS|2026-07-21 @ Kansas City Royals: 4 FS|2026-07-20 @ Kansas City Royals: 14 FS|2026-07-19 @ Seattle Mariners: 5 FS|2026-07-18 @ Seattle Mariners: 3 FS</t>
+          <t>2026-07-22 @ Arizona Diamondbacks: 6 FS|2026-07-21 @ Arizona Diamondbacks: 16 FS|2026-07-20 @ Arizona Diamondbacks: 7 FS|2026-07-19 vs Washington Nationals: 8 FS|2026-07-18 vs Washington Nationals: 15 FS</t>
         </is>
       </c>
       <c r="DF27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Kansas City Royals: 0 FS|2026-07-21 @ Kansas City Royals: 4 FS|2026-07-20 @ Kansas City Royals: 14 FS|2026-07-19 @ Seattle Mariners: 5 FS|2026-07-18 @ Seattle Mariners: 3 FS|2026-07-17 @ Seattle Mariners: 8 FS|2026-07-12 vs Colorado Rockies: 6 FS|2026-07-11 vs Colorado Rockies: 5 FS|2026-07-10 vs Colorado Rockies: 0 FS|2026-07-09 vs Colorado Rockies: 5 FS</t>
+          <t>2026-07-22 @ Arizona Diamondbacks: 6 FS|2026-07-21 @ Arizona Diamondbacks: 16 FS|2026-07-20 @ Arizona Diamondbacks: 7 FS|2026-07-19 vs Washington Nationals: 8 FS|2026-07-18 vs Washington Nationals: 15 FS|2026-07-17 vs Washington Nationals: 14 FS|2026-07-12 @ Chicago White Sox: 14 FS|2026-07-11 @ Chicago White Sox: 0 FS|2026-07-10 @ Chicago White Sox: 0 FS|2026-07-09 @ Detroit Tigers: 7 FS</t>
         </is>
       </c>
       <c r="DG27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Kansas City Royals: 0 FS|2026-07-21 @ Kansas City Royals: 4 FS|2026-07-20 @ Kansas City Royals: 14 FS|2026-07-19 @ Seattle Mariners: 5 FS|2026-07-18 @ Seattle Mariners: 3 FS|2026-07-17 @ Seattle Mariners: 8 FS|2026-07-12 vs Colorado Rockies: 6 FS|2026-07-11 vs Colorado Rockies: 5 FS|2026-07-10 vs Colorado Rockies: 0 FS|2026-07-09 vs Colorado Rockies: 5 FS|2026-07-08 vs Toronto Blue Jays: 3 FS|2026-07-07 vs Toronto Blue Jays: 10 FS|2026-07-06 vs Toronto Blue Jays: 44 FS|2026-07-05 @ Colorado Rockies: 5 FS|2026-07-04 @ Colorado Rockies: 7 FS</t>
+          <t>2026-07-22 @ Arizona Diamondbacks: 6 FS|2026-07-21 @ Arizona Diamondbacks: 16 FS|2026-07-20 @ Arizona Diamondbacks: 7 FS|2026-07-19 vs Washington Nationals: 8 FS|2026-07-18 vs Washington Nationals: 15 FS|2026-07-17 vs Washington Nationals: 14 FS|2026-07-12 @ Chicago White Sox: 14 FS|2026-07-11 @ Chicago White Sox: 0 FS|2026-07-10 @ Chicago White Sox: 0 FS|2026-07-09 @ Detroit Tigers: 7 FS|2026-07-08 @ Detroit Tigers: 0 FS|2026-07-07 @ Detroit Tigers: 7 FS|2026-07-03 vs Miami Marlins: 0 FS|2026-07-01 vs Los Angeles Dodgers: 17 FS|2026-06-30 vs Los Angeles Dodgers: 5 FS</t>
         </is>
       </c>
       <c r="DH27" s="3" t="n">
@@ -25234,10 +25234,10 @@
         <v>30</v>
       </c>
       <c r="DJ27" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>7.07</v>
       </c>
       <c r="DK27" s="3" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="DL27" s="4" t="inlineStr">
         <is>
@@ -25245,13 +25245,13 @@
         </is>
       </c>
       <c r="DM27" s="3" t="n">
-        <v>5.71</v>
+        <v>11.43</v>
       </c>
       <c r="DN27" s="3" t="n">
-        <v>8</v>
+        <v>7.93</v>
       </c>
       <c r="DO27" s="3" t="n">
-        <v>0.276</v>
+        <v>0.265</v>
       </c>
       <c r="DP27" s="4" t="inlineStr">
         <is>
@@ -25259,40 +25259,40 @@
         </is>
       </c>
       <c r="DQ27" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>7.07</v>
       </c>
       <c r="DR27" s="3" t="n">
-        <v>1.867</v>
+        <v>1.982</v>
       </c>
       <c r="DS27" s="3" t="n">
-        <v>0.2667</v>
+        <v>0.2321</v>
       </c>
       <c r="DT27" s="3" t="n">
-        <v>0.0667</v>
+        <v>0.1071</v>
       </c>
       <c r="DU27" s="3" t="n">
-        <v>0.05</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="DV27" s="3" t="n">
-        <v>0.0167</v>
+        <v>0.1071</v>
       </c>
       <c r="DW27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="DX27" s="3" t="n">
-        <v>10.2</v>
+        <v>11.18</v>
       </c>
       <c r="DY27" s="3" t="n">
-        <v>10.61</v>
+        <v>10.15</v>
       </c>
       <c r="DZ27" s="3" t="n">
-        <v>10.23</v>
+        <v>10.94</v>
       </c>
       <c r="EA27" s="3" t="n">
-        <v>9.619999999999999</v>
+        <v>11.65</v>
       </c>
       <c r="EB27" s="3" t="n">
-        <v>9.279999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="EC27" s="3" t="n">
         <v>28</v>
@@ -25315,13 +25315,13 @@
         </is>
       </c>
       <c r="EI27" s="3" t="n">
-        <v>19.42</v>
+        <v>24</v>
       </c>
       <c r="EJ27" s="3" t="n">
-        <v>57.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="EK27" s="3" t="n">
-        <v>42.9</v>
+        <v>29.4</v>
       </c>
       <c r="EL27" s="4" t="inlineStr">
         <is>
@@ -25334,25 +25334,25 @@
         </is>
       </c>
       <c r="EN27" s="3" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="EO27" s="3" t="n">
-        <v>33.5</v>
+        <v>36.4</v>
       </c>
       <c r="EP27" s="3" t="n">
-        <v>54.4</v>
+        <v>62.6</v>
       </c>
       <c r="EQ27" s="3" t="n">
-        <v>49.8</v>
+        <v>69</v>
       </c>
       <c r="ER27" s="3" t="n">
-        <v>1.0652</v>
+        <v>1.108</v>
       </c>
       <c r="ES27" s="3" t="n">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="ET27" s="3" t="n">
-        <v>2.68</v>
+        <v>-0.74</v>
       </c>
       <c r="EU27" s="3" t="n">
         <v>1</v>
@@ -25367,25 +25367,25 @@
         <v>75</v>
       </c>
       <c r="EY27" s="3" t="n">
-        <v>109</v>
+        <v>245</v>
       </c>
       <c r="EZ27" s="3" t="n">
-        <v>87.20999999999999</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="FA27" s="3" t="n">
-        <v>33.94</v>
+        <v>28.16</v>
       </c>
       <c r="FB27" s="3" t="n">
-        <v>4.59</v>
+        <v>4.08</v>
       </c>
       <c r="FC27" s="3" t="n">
-        <v>39.45</v>
+        <v>32.24</v>
       </c>
       <c r="FD27" s="3" t="n">
-        <v>0.497</v>
+        <v>0.418</v>
       </c>
       <c r="FE27" s="3" t="n">
-        <v>1.1018</v>
+        <v>0.9956</v>
       </c>
       <c r="FF27" s="3" t="n">
         <v>1</v>
@@ -25397,10 +25397,10 @@
         <v>1</v>
       </c>
       <c r="FI27" s="3" t="n">
-        <v>0.9881</v>
+        <v>1.0331</v>
       </c>
       <c r="FJ27" s="3" t="n">
-        <v>186</v>
+        <v>541</v>
       </c>
       <c r="FK27" s="4" t="inlineStr">
         <is>
@@ -25408,10 +25408,10 @@
         </is>
       </c>
       <c r="FL27" s="3" t="n">
-        <v>1.14</v>
+        <v>0.9474</v>
       </c>
       <c r="FM27" s="3" t="n">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="FN27" s="4" t="inlineStr">
         <is>
@@ -25419,52 +25419,52 @@
         </is>
       </c>
       <c r="FO27" s="3" t="n">
-        <v>109</v>
+        <v>245</v>
       </c>
       <c r="FP27" s="3" t="n">
-        <v>87.20999999999999</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="FQ27" s="3" t="n">
         <v>12</v>
       </c>
       <c r="FR27" s="3" t="n">
-        <v>14.11</v>
+        <v>24.6</v>
       </c>
       <c r="FS27" s="3" t="n">
-        <v>31.24</v>
+        <v>31.33</v>
       </c>
       <c r="FT27" s="3" t="n">
-        <v>11.9</v>
+        <v>23.3</v>
       </c>
       <c r="FU27" s="3" t="n">
-        <v>69.7</v>
+        <v>63.3</v>
       </c>
       <c r="FV27" s="3" t="n">
-        <v>18.4</v>
+        <v>13.5</v>
       </c>
       <c r="FW27" s="3" t="n">
-        <v>0.9782999999999999</v>
+        <v>1.0286</v>
       </c>
       <c r="FX27" s="3" t="n">
-        <v>1.0086</v>
+        <v>1.0068</v>
       </c>
       <c r="FY27" s="3" t="n">
-        <v>1.0495</v>
+        <v>1.0543</v>
       </c>
       <c r="FZ27" s="3" t="n">
-        <v>1.2512</v>
+        <v>1.0136</v>
       </c>
       <c r="GA27" s="3" t="n">
-        <v>0.9103</v>
+        <v>1.0754</v>
       </c>
       <c r="GB27" s="3" t="n">
-        <v>0.984</v>
+        <v>1.0131</v>
       </c>
       <c r="GC27" s="3" t="n">
-        <v>6.8</v>
+        <v>8.16</v>
       </c>
       <c r="GD27" s="3" t="n">
-        <v>-1.34</v>
+        <v>1.09</v>
       </c>
       <c r="GE27" s="4" t="inlineStr">
         <is>
@@ -25509,52 +25509,52 @@
         <v>27</v>
       </c>
       <c r="GQ27" s="3" t="n">
-        <v>0.8625</v>
+        <v>0.89</v>
       </c>
       <c r="GR27" s="3" t="n">
         <v>27</v>
       </c>
       <c r="GS27" s="3" t="n">
-        <v>0.984</v>
+        <v>1</v>
       </c>
       <c r="GT27" s="3" t="n">
-        <v>0.2344</v>
+        <v>0.146</v>
       </c>
       <c r="GU27" s="3" t="n">
-        <v>0.055</v>
+        <v>0.0465</v>
       </c>
       <c r="GV27" s="3" t="n">
-        <v>0.012</v>
+        <v>0.0002</v>
       </c>
       <c r="GW27" s="3" t="n">
-        <v>0.0437</v>
+        <v>0.0717</v>
       </c>
       <c r="GX27" s="3" t="n">
-        <v>0.0475</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="GY27" s="3" t="n">
-        <v>0.0094</v>
+        <v>0.0111</v>
       </c>
       <c r="GZ27" s="3" t="n">
-        <v>0.2393</v>
+        <v>0.2192</v>
       </c>
       <c r="HA27" s="3" t="n">
-        <v>0.5345</v>
+        <v>0.3867</v>
       </c>
       <c r="HB27" s="3" t="n">
-        <v>0.2413</v>
+        <v>0.3613</v>
       </c>
       <c r="HC27" s="3" t="n">
-        <v>0.2242</v>
+        <v>0.252</v>
       </c>
       <c r="HD27" s="3" t="n">
-        <v>0.0786</v>
+        <v>0.0358</v>
       </c>
       <c r="HE27" s="3" t="n">
-        <v>0.1553</v>
+        <v>0.1299</v>
       </c>
       <c r="HF27" s="3" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0018</v>
       </c>
       <c r="HG27" s="3" t="n">
         <v>1</v>
@@ -25566,19 +25566,19 @@
       </c>
       <c r="HI27" s="4" t="n"/>
       <c r="HJ27" s="3" t="n">
-        <v>6.98</v>
+        <v>6.41</v>
       </c>
       <c r="HK27" s="3" t="n">
-        <v>3.73</v>
+        <v>4.87</v>
       </c>
       <c r="HL27" s="3" t="n">
-        <v>13.51</v>
+        <v>14.23</v>
       </c>
       <c r="HM27" s="3" t="n">
-        <v>19.73</v>
+        <v>18.55</v>
       </c>
       <c r="HN27" s="3" t="n">
-        <v>4.27</v>
+        <v>4.41</v>
       </c>
       <c r="HO27" s="3" t="n">
         <v>0</v>
@@ -25594,97 +25594,97 @@
         </is>
       </c>
       <c r="HR27" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="HS27" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="HT27" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="HU27" s="3" t="n">
-        <v>74.2</v>
+        <v>84.7</v>
       </c>
       <c r="HV27" s="3" t="n">
-        <v>74.2</v>
+        <v>77.8</v>
       </c>
       <c r="HW27" s="3" t="n">
-        <v>72.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="HX27" s="3" t="n">
-        <v>72.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="HY27" s="3" t="n">
-        <v>61.7</v>
+        <v>65</v>
       </c>
       <c r="HZ27" s="3" t="n">
-        <v>58</v>
+        <v>55.8</v>
       </c>
       <c r="IA27" s="3" t="n">
-        <v>58</v>
+        <v>55.8</v>
       </c>
       <c r="IB27" s="3" t="n">
-        <v>51.8</v>
+        <v>52.7</v>
       </c>
       <c r="IC27" s="3" t="n">
-        <v>51.8</v>
+        <v>46.4</v>
       </c>
       <c r="ID27" s="3" t="n">
-        <v>45.7</v>
+        <v>42.8</v>
       </c>
       <c r="IE27" s="3" t="n">
-        <v>45.7</v>
+        <v>42.8</v>
       </c>
       <c r="IF27" s="3" t="n">
-        <v>42</v>
+        <v>39.6</v>
       </c>
       <c r="IG27" s="3" t="n">
-        <v>35.8</v>
+        <v>36.6</v>
       </c>
       <c r="IH27" s="3" t="n">
-        <v>35.8</v>
+        <v>36.6</v>
       </c>
       <c r="II27" s="3" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="IJ27" s="3" t="n">
-        <v>33.3</v>
+        <v>32.7</v>
       </c>
       <c r="IK27" s="3" t="n">
-        <v>29.2</v>
+        <v>32.7</v>
       </c>
       <c r="IL27" s="3" t="n">
-        <v>29.2</v>
+        <v>31.6</v>
       </c>
       <c r="IM27" s="3" t="n">
-        <v>26.5</v>
+        <v>26.9</v>
       </c>
       <c r="IN27" s="3" t="n">
-        <v>26.5</v>
+        <v>26.9</v>
       </c>
       <c r="IO27" s="3" t="n">
-        <v>22.7</v>
+        <v>26.1</v>
       </c>
       <c r="IP27" s="3" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="IQ27" s="3" t="n">
-        <v>20.7</v>
+        <v>20</v>
       </c>
       <c r="IR27" s="3" t="n">
-        <v>18.3</v>
+        <v>20</v>
       </c>
       <c r="IS27" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="IT27" s="3" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="IU27" s="3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="IV27" s="3" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="IW27" s="3" t="n">
         <v>6</v>
@@ -25770,168 +25770,168 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Shea Langeliers</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>ATH @ MIN</t>
+          <t>LAA @ SF</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LF</t>
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>9.42</v>
+        <v>9.48</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>9.67</v>
+        <v>9.57</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>9.67</v>
+        <v>9.57</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>7.75</v>
+        <v>8.18</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>5.59</v>
+        <v>7.51</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>5.75</v>
+        <v>6.98</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>8.91</v>
+        <v>7.86</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>6.41</v>
+        <v>6.98</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.72</v>
+        <v>0.888</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>10.4</v>
+        <v>5.2</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>7.73</v>
+        <v>7.93</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>6|16|7|8|15</t>
+          <t>0|4|14|5|3</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>6|16|7|8|15|14|14|0|0|7</t>
+          <t>0|4|14|5|3|8|6|5|0|5</t>
         </is>
       </c>
       <c r="X28" s="4" t="inlineStr">
         <is>
-          <t>6|16|7|8|15|14|14|0|0|7|0|7|0|17|5</t>
+          <t>0|4|14|5|3|8|6|5|0|5|3|10|44|5|7</t>
         </is>
       </c>
       <c r="Y28" s="5" t="n">
-        <v>99.5</v>
+        <v>92.5</v>
       </c>
       <c r="Z28" s="5" t="n">
-        <v>90.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AA28" s="5" t="n">
-        <v>90.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="AB28" s="5" t="n">
-        <v>90</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>83.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AD28" s="5" t="n">
-        <v>73.5</v>
+        <v>77.7</v>
       </c>
       <c r="AE28" s="5" t="n">
-        <v>73</v>
+        <v>77.2</v>
       </c>
       <c r="AF28" s="5" t="n">
-        <v>68.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="AG28" s="5" t="n">
-        <v>59.4</v>
+        <v>61.5</v>
       </c>
       <c r="AH28" s="5" t="n">
-        <v>58.9</v>
+        <v>61</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>55.2</v>
+        <v>54.3</v>
       </c>
       <c r="AJ28" s="7" t="n">
-        <v>47.5</v>
+        <v>52.8</v>
       </c>
       <c r="AK28" s="7" t="n">
-        <v>42.8</v>
+        <v>45.8</v>
       </c>
       <c r="AL28" s="7" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="AM28" s="8" t="n">
-        <v>39.6</v>
+        <v>45.8</v>
+      </c>
+      <c r="AM28" s="7" t="n">
+        <v>42</v>
       </c>
       <c r="AN28" s="8" t="n">
-        <v>36.6</v>
+        <v>35.8</v>
       </c>
       <c r="AO28" s="8" t="n">
-        <v>36.6</v>
+        <v>35.8</v>
       </c>
       <c r="AP28" s="8" t="n">
-        <v>35</v>
+        <v>33.4</v>
       </c>
       <c r="AQ28" s="8" t="n">
-        <v>32.7</v>
+        <v>33.4</v>
       </c>
       <c r="AR28" s="8" t="n">
-        <v>32.7</v>
+        <v>29.3</v>
       </c>
       <c r="AS28" s="8" t="n">
-        <v>31.6</v>
+        <v>29.3</v>
       </c>
       <c r="AT28" s="8" t="n">
-        <v>26.9</v>
+        <v>26.6</v>
       </c>
       <c r="AU28" s="8" t="n">
-        <v>26.9</v>
+        <v>26.6</v>
       </c>
       <c r="AV28" s="8" t="n">
-        <v>26.1</v>
+        <v>22.8</v>
       </c>
       <c r="AW28" s="8" t="n">
-        <v>21.8</v>
+        <v>20.8</v>
       </c>
       <c r="AX28" s="8" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="AY28" s="8" t="n">
-        <v>20</v>
+        <v>18.3</v>
       </c>
       <c r="AZ28" s="3" t="n">
-        <v>236.73</v>
+        <v>236.77</v>
       </c>
       <c r="BA28" s="4" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
       </c>
       <c r="BB28" s="9" t="inlineStr">
         <is>
-          <t>MORE 7.0 | 58.9% | Edge +2.7</t>
+          <t>MORE 7.0 | 61.0% | Edge +2.6</t>
         </is>
       </c>
       <c r="BC28" s="4" t="inlineStr">
@@ -25952,13 +25952,13 @@
         <v>7</v>
       </c>
       <c r="BE28" s="3" t="n">
-        <v>58.9</v>
+        <v>61</v>
       </c>
       <c r="BF28" s="3" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="BG28" s="3" t="n">
-        <v>17.8</v>
+        <v>22</v>
       </c>
       <c r="BH28" s="4" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         </is>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BJ28" s="4" t="inlineStr">
         <is>
@@ -25975,24 +25975,24 @@
       </c>
       <c r="BK28" s="4" t="n"/>
       <c r="BL28" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BM28" s="3" t="n">
         <v>7</v>
       </c>
       <c r="BN28" s="4" t="inlineStr">
         <is>
-          <t>3-3-3-3-3-4-3</t>
+          <t>3-1-5-5-5-5-1</t>
         </is>
       </c>
       <c r="BO28" s="3" t="n">
-        <v>85.7</v>
+        <v>57.1</v>
       </c>
       <c r="BP28" s="3" t="n">
         <v>97</v>
       </c>
       <c r="BQ28" s="3" t="n">
-        <v>4.92</v>
+        <v>4.52</v>
       </c>
       <c r="BR28" s="4" t="inlineStr">
         <is>
@@ -26000,14 +26000,14 @@
         </is>
       </c>
       <c r="BS28" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BT28" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="BU28" s="4" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="BV28" s="4" t="inlineStr">
@@ -26016,124 +26016,124 @@
         </is>
       </c>
       <c r="BW28" s="3" t="n">
-        <v>5.4</v>
+        <v>8.23</v>
       </c>
       <c r="BX28" s="3" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="BY28" s="3" t="n">
-        <v>0.2458</v>
+        <v>0.2679</v>
       </c>
       <c r="BZ28" s="3" t="n">
-        <v>0.0505</v>
+        <v>0.0298</v>
       </c>
       <c r="CA28" s="3" t="n">
-        <v>0.0707</v>
+        <v>0.1012</v>
       </c>
       <c r="CB28" s="3" t="n">
-        <v>4.71</v>
+        <v>4.52</v>
       </c>
       <c r="CC28" s="3" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="CD28" s="3" t="n">
-        <v>0.2235</v>
+        <v>0.2038</v>
       </c>
       <c r="CE28" s="3" t="n">
-        <v>0.0313</v>
+        <v>0.0278</v>
       </c>
       <c r="CF28" s="4" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="CG28" s="3" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CH28" s="3" t="n">
-        <v>1</v>
+        <v>1.025</v>
       </c>
       <c r="CI28" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="CJ28" s="3" t="n">
-        <v>6.8</v>
+        <v>17.6</v>
       </c>
       <c r="CK28" s="3" t="n">
-        <v>188</v>
+        <v>285</v>
       </c>
       <c r="CL28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CM28" s="4" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>windy</t>
         </is>
       </c>
       <c r="CN28" s="3" t="n">
-        <v>412</v>
+        <v>260</v>
       </c>
       <c r="CO28" s="3" t="n">
-        <v>372</v>
+        <v>246</v>
       </c>
       <c r="CP28" s="3" t="n">
-        <v>0.263</v>
+        <v>0.268</v>
       </c>
       <c r="CQ28" s="3" t="n">
-        <v>0.333</v>
+        <v>0.304</v>
       </c>
       <c r="CR28" s="3" t="n">
-        <v>0.497</v>
+        <v>0.455</v>
       </c>
       <c r="CS28" s="3" t="n">
-        <v>0.83</v>
+        <v>0.759</v>
       </c>
       <c r="CT28" s="3" t="n">
-        <v>285</v>
+        <v>203</v>
       </c>
       <c r="CU28" s="3" t="n">
-        <v>0.747</v>
+        <v>0.718</v>
       </c>
       <c r="CV28" s="3" t="n">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="CW28" s="3" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="CX28" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CY28" s="3" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="CZ28" s="3" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="DA28" s="3" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="DB28" s="3" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="DC28" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="DD28" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DE28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Arizona Diamondbacks: 6 FS|2026-07-21 @ Arizona Diamondbacks: 16 FS|2026-07-20 @ Arizona Diamondbacks: 7 FS|2026-07-19 vs Washington Nationals: 8 FS|2026-07-18 vs Washington Nationals: 15 FS</t>
+          <t>2026-07-22 @ Kansas City Royals: 0 FS|2026-07-21 @ Kansas City Royals: 4 FS|2026-07-20 @ Kansas City Royals: 14 FS|2026-07-19 @ Seattle Mariners: 5 FS|2026-07-18 @ Seattle Mariners: 3 FS</t>
         </is>
       </c>
       <c r="DF28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Arizona Diamondbacks: 6 FS|2026-07-21 @ Arizona Diamondbacks: 16 FS|2026-07-20 @ Arizona Diamondbacks: 7 FS|2026-07-19 vs Washington Nationals: 8 FS|2026-07-18 vs Washington Nationals: 15 FS|2026-07-17 vs Washington Nationals: 14 FS|2026-07-12 @ Chicago White Sox: 14 FS|2026-07-11 @ Chicago White Sox: 0 FS|2026-07-10 @ Chicago White Sox: 0 FS|2026-07-09 @ Detroit Tigers: 7 FS</t>
+          <t>2026-07-22 @ Kansas City Royals: 0 FS|2026-07-21 @ Kansas City Royals: 4 FS|2026-07-20 @ Kansas City Royals: 14 FS|2026-07-19 @ Seattle Mariners: 5 FS|2026-07-18 @ Seattle Mariners: 3 FS|2026-07-17 @ Seattle Mariners: 8 FS|2026-07-12 vs Colorado Rockies: 6 FS|2026-07-11 vs Colorado Rockies: 5 FS|2026-07-10 vs Colorado Rockies: 0 FS|2026-07-09 vs Colorado Rockies: 5 FS</t>
         </is>
       </c>
       <c r="DG28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22 @ Arizona Diamondbacks: 6 FS|2026-07-21 @ Arizona Diamondbacks: 16 FS|2026-07-20 @ Arizona Diamondbacks: 7 FS|2026-07-19 vs Washington Nationals: 8 FS|2026-07-18 vs Washington Nationals: 15 FS|2026-07-17 vs Washington Nationals: 14 FS|2026-07-12 @ Chicago White Sox: 14 FS|2026-07-11 @ Chicago White Sox: 0 FS|2026-07-10 @ Chicago White Sox: 0 FS|2026-07-09 @ Detroit Tigers: 7 FS|2026-07-08 @ Detroit Tigers: 0 FS|2026-07-07 @ Detroit Tigers: 7 FS|2026-07-03 vs Miami Marlins: 0 FS|2026-07-01 vs Los Angeles Dodgers: 17 FS|2026-06-30 vs Los Angeles Dodgers: 5 FS</t>
+          <t>2026-07-22 @ Kansas City Royals: 0 FS|2026-07-21 @ Kansas City Royals: 4 FS|2026-07-20 @ Kansas City Royals: 14 FS|2026-07-19 @ Seattle Mariners: 5 FS|2026-07-18 @ Seattle Mariners: 3 FS|2026-07-17 @ Seattle Mariners: 8 FS|2026-07-12 vs Colorado Rockies: 6 FS|2026-07-11 vs Colorado Rockies: 5 FS|2026-07-10 vs Colorado Rockies: 0 FS|2026-07-09 vs Colorado Rockies: 5 FS|2026-07-08 vs Toronto Blue Jays: 3 FS|2026-07-07 vs Toronto Blue Jays: 10 FS|2026-07-06 vs Toronto Blue Jays: 44 FS|2026-07-05 @ Colorado Rockies: 5 FS|2026-07-04 @ Colorado Rockies: 7 FS</t>
         </is>
       </c>
       <c r="DH28" s="3" t="n">
@@ -26143,10 +26143,10 @@
         <v>30</v>
       </c>
       <c r="DJ28" s="3" t="n">
-        <v>7.07</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DK28" s="3" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="DL28" s="4" t="inlineStr">
         <is>
@@ -26154,13 +26154,13 @@
         </is>
       </c>
       <c r="DM28" s="3" t="n">
-        <v>11.43</v>
+        <v>5.71</v>
       </c>
       <c r="DN28" s="3" t="n">
-        <v>7.93</v>
+        <v>8</v>
       </c>
       <c r="DO28" s="3" t="n">
-        <v>0.265</v>
+        <v>0.276</v>
       </c>
       <c r="DP28" s="4" t="inlineStr">
         <is>
@@ -26168,40 +26168,40 @@
         </is>
       </c>
       <c r="DQ28" s="3" t="n">
-        <v>7.07</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DR28" s="3" t="n">
-        <v>1.982</v>
+        <v>1.867</v>
       </c>
       <c r="DS28" s="3" t="n">
-        <v>0.2321</v>
+        <v>0.2667</v>
       </c>
       <c r="DT28" s="3" t="n">
-        <v>0.1071</v>
+        <v>0.0667</v>
       </c>
       <c r="DU28" s="3" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="DV28" s="3" t="n">
-        <v>0.1071</v>
+        <v>0.0167</v>
       </c>
       <c r="DW28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="DX28" s="3" t="n">
-        <v>11.18</v>
+        <v>10.2</v>
       </c>
       <c r="DY28" s="3" t="n">
-        <v>10.15</v>
+        <v>10.61</v>
       </c>
       <c r="DZ28" s="3" t="n">
-        <v>10.94</v>
+        <v>10.23</v>
       </c>
       <c r="EA28" s="3" t="n">
-        <v>11.65</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="EB28" s="3" t="n">
-        <v>9.48</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="EC28" s="3" t="n">
         <v>28</v>
@@ -26224,13 +26224,13 @@
         </is>
       </c>
       <c r="EI28" s="3" t="n">
-        <v>24</v>
+        <v>19.42</v>
       </c>
       <c r="EJ28" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>57.1</v>
       </c>
       <c r="EK28" s="3" t="n">
-        <v>29.4</v>
+        <v>42.9</v>
       </c>
       <c r="EL28" s="4" t="inlineStr">
         <is>
@@ -26243,25 +26243,25 @@
         </is>
       </c>
       <c r="EN28" s="3" t="n">
-        <v>47.9</v>
+        <v>44.6</v>
       </c>
       <c r="EO28" s="3" t="n">
-        <v>36.4</v>
+        <v>33.5</v>
       </c>
       <c r="EP28" s="3" t="n">
-        <v>62.6</v>
+        <v>54.4</v>
       </c>
       <c r="EQ28" s="3" t="n">
-        <v>69</v>
+        <v>49.8</v>
       </c>
       <c r="ER28" s="3" t="n">
-        <v>1.108</v>
+        <v>1.0652</v>
       </c>
       <c r="ES28" s="3" t="n">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="ET28" s="3" t="n">
-        <v>-0.74</v>
+        <v>2.68</v>
       </c>
       <c r="EU28" s="3" t="n">
         <v>1</v>
@@ -26276,25 +26276,25 @@
         <v>75</v>
       </c>
       <c r="EY28" s="3" t="n">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="EZ28" s="3" t="n">
-        <v>85.06999999999999</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="FA28" s="3" t="n">
-        <v>28.16</v>
+        <v>33.94</v>
       </c>
       <c r="FB28" s="3" t="n">
-        <v>4.08</v>
+        <v>4.59</v>
       </c>
       <c r="FC28" s="3" t="n">
-        <v>32.24</v>
+        <v>39.45</v>
       </c>
       <c r="FD28" s="3" t="n">
-        <v>0.418</v>
+        <v>0.497</v>
       </c>
       <c r="FE28" s="3" t="n">
-        <v>0.9956</v>
+        <v>1.1018</v>
       </c>
       <c r="FF28" s="3" t="n">
         <v>1</v>
@@ -26306,10 +26306,10 @@
         <v>1</v>
       </c>
       <c r="FI28" s="3" t="n">
-        <v>1.0331</v>
+        <v>0.9881</v>
       </c>
       <c r="FJ28" s="3" t="n">
-        <v>541</v>
+        <v>186</v>
       </c>
       <c r="FK28" s="4" t="inlineStr">
         <is>
@@ -26317,10 +26317,10 @@
         </is>
       </c>
       <c r="FL28" s="3" t="n">
-        <v>0.9474</v>
+        <v>1.14</v>
       </c>
       <c r="FM28" s="3" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="FN28" s="4" t="inlineStr">
         <is>
@@ -26328,52 +26328,52 @@
         </is>
       </c>
       <c r="FO28" s="3" t="n">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="FP28" s="3" t="n">
-        <v>85.06999999999999</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="FQ28" s="3" t="n">
         <v>12</v>
       </c>
       <c r="FR28" s="3" t="n">
-        <v>24.6</v>
+        <v>14.11</v>
       </c>
       <c r="FS28" s="3" t="n">
-        <v>31.33</v>
+        <v>31.24</v>
       </c>
       <c r="FT28" s="3" t="n">
-        <v>23.3</v>
+        <v>11.9</v>
       </c>
       <c r="FU28" s="3" t="n">
-        <v>63.3</v>
+        <v>69.7</v>
       </c>
       <c r="FV28" s="3" t="n">
-        <v>13.5</v>
+        <v>18.4</v>
       </c>
       <c r="FW28" s="3" t="n">
-        <v>1.0286</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="FX28" s="3" t="n">
-        <v>1.0068</v>
+        <v>1.0086</v>
       </c>
       <c r="FY28" s="3" t="n">
-        <v>1.0543</v>
+        <v>1.0495</v>
       </c>
       <c r="FZ28" s="3" t="n">
-        <v>1.0136</v>
+        <v>1.2512</v>
       </c>
       <c r="GA28" s="3" t="n">
-        <v>1.0754</v>
+        <v>0.9103</v>
       </c>
       <c r="GB28" s="3" t="n">
-        <v>1.0131</v>
+        <v>0.984</v>
       </c>
       <c r="GC28" s="3" t="n">
-        <v>8.16</v>
+        <v>6.8</v>
       </c>
       <c r="GD28" s="3" t="n">
-        <v>1.09</v>
+        <v>-1.34</v>
       </c>
       <c r="GE28" s="4" t="inlineStr">
         <is>
@@ -26418,52 +26418,52 @@
         <v>27</v>
       </c>
       <c r="GQ28" s="3" t="n">
-        <v>0.89</v>
+        <v>0.8625</v>
       </c>
       <c r="GR28" s="3" t="n">
         <v>27</v>
       </c>
       <c r="GS28" s="3" t="n">
-        <v>1</v>
+        <v>0.984</v>
       </c>
       <c r="GT28" s="3" t="n">
-        <v>0.146</v>
+        <v>0.2344</v>
       </c>
       <c r="GU28" s="3" t="n">
-        <v>0.0465</v>
+        <v>0.055</v>
       </c>
       <c r="GV28" s="3" t="n">
-        <v>0.0002</v>
+        <v>0.012</v>
       </c>
       <c r="GW28" s="3" t="n">
-        <v>0.0717</v>
+        <v>0.0437</v>
       </c>
       <c r="GX28" s="3" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0475</v>
       </c>
       <c r="GY28" s="3" t="n">
-        <v>0.0111</v>
+        <v>0.0094</v>
       </c>
       <c r="GZ28" s="3" t="n">
-        <v>0.2192</v>
+        <v>0.2393</v>
       </c>
       <c r="HA28" s="3" t="n">
-        <v>0.3867</v>
+        <v>0.5345</v>
       </c>
       <c r="HB28" s="3" t="n">
-        <v>0.3613</v>
+        <v>0.2413</v>
       </c>
       <c r="HC28" s="3" t="n">
-        <v>0.252</v>
+        <v>0.2242</v>
       </c>
       <c r="HD28" s="3" t="n">
-        <v>0.0358</v>
+        <v>0.0786</v>
       </c>
       <c r="HE28" s="3" t="n">
-        <v>0.1299</v>
+        <v>0.1553</v>
       </c>
       <c r="HF28" s="3" t="n">
-        <v>0.0018</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="HG28" s="3" t="n">
         <v>1</v>
@@ -26475,19 +26475,19 @@
       </c>
       <c r="HI28" s="4" t="n"/>
       <c r="HJ28" s="3" t="n">
-        <v>6.41</v>
+        <v>6.98</v>
       </c>
       <c r="HK28" s="3" t="n">
-        <v>4.87</v>
+        <v>3.74</v>
       </c>
       <c r="HL28" s="3" t="n">
-        <v>14.23</v>
+        <v>13.5</v>
       </c>
       <c r="HM28" s="3" t="n">
-        <v>18.55</v>
+        <v>19.72</v>
       </c>
       <c r="HN28" s="3" t="n">
-        <v>4.41</v>
+        <v>4.27</v>
       </c>
       <c r="HO28" s="3" t="n">
         <v>0</v>
@@ -26503,97 +26503,97 @@
         </is>
       </c>
       <c r="HR28" s="3" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="HS28" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="HT28" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="HU28" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="HV28" s="3" t="n">
-        <v>77.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="HW28" s="3" t="n">
-        <v>68.5</v>
+        <v>72.7</v>
       </c>
       <c r="HX28" s="3" t="n">
-        <v>68.5</v>
+        <v>72.7</v>
       </c>
       <c r="HY28" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>61.7</v>
       </c>
       <c r="HZ28" s="3" t="n">
-        <v>55.9</v>
+        <v>58</v>
       </c>
       <c r="IA28" s="3" t="n">
-        <v>55.9</v>
+        <v>58</v>
       </c>
       <c r="IB28" s="3" t="n">
-        <v>52.7</v>
+        <v>51.8</v>
       </c>
       <c r="IC28" s="3" t="n">
-        <v>46.5</v>
+        <v>51.8</v>
       </c>
       <c r="ID28" s="3" t="n">
-        <v>42.8</v>
+        <v>45.8</v>
       </c>
       <c r="IE28" s="3" t="n">
-        <v>42.8</v>
+        <v>45.8</v>
       </c>
       <c r="IF28" s="3" t="n">
-        <v>39.6</v>
+        <v>42</v>
       </c>
       <c r="IG28" s="3" t="n">
-        <v>36.6</v>
+        <v>35.8</v>
       </c>
       <c r="IH28" s="3" t="n">
-        <v>36.6</v>
+        <v>35.8</v>
       </c>
       <c r="II28" s="3" t="n">
-        <v>35</v>
+        <v>33.4</v>
       </c>
       <c r="IJ28" s="3" t="n">
-        <v>32.7</v>
+        <v>33.4</v>
       </c>
       <c r="IK28" s="3" t="n">
-        <v>32.7</v>
+        <v>29.3</v>
       </c>
       <c r="IL28" s="3" t="n">
-        <v>31.6</v>
+        <v>29.3</v>
       </c>
       <c r="IM28" s="3" t="n">
-        <v>26.9</v>
+        <v>26.6</v>
       </c>
       <c r="IN28" s="3" t="n">
-        <v>26.9</v>
+        <v>26.6</v>
       </c>
       <c r="IO28" s="3" t="n">
-        <v>26.1</v>
+        <v>22.8</v>
       </c>
       <c r="IP28" s="3" t="n">
-        <v>21.8</v>
+        <v>20.8</v>
       </c>
       <c r="IQ28" s="3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="IR28" s="3" t="n">
-        <v>20</v>
+        <v>18.3</v>
       </c>
       <c r="IS28" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="IT28" s="3" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="IU28" s="3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="IV28" s="3" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="IW28" s="3" t="n">
         <v>6</v>
@@ -26726,13 +26726,13 @@
         <v>6.46</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8.49</v>
+        <v>8.48</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>6.46</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>8.800000000000001</v>
@@ -28521,13 +28521,13 @@
         <v>9.16</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>9.51</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>9.51</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>6.9</v>
+        <v>6.88</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>6.95</v>
@@ -28536,13 +28536,13 @@
         <v>6.61</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>8.9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>6.61</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>6.2</v>
@@ -28569,88 +28569,88 @@
         </is>
       </c>
       <c r="Y31" s="5" t="n">
-        <v>92.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="Z31" s="5" t="n">
-        <v>92.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="AA31" s="5" t="n">
-        <v>91.8</v>
+        <v>91.7</v>
       </c>
       <c r="AB31" s="5" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>80.7</v>
+        <v>80.5</v>
       </c>
       <c r="AD31" s="5" t="n">
-        <v>75.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="AE31" s="5" t="n">
-        <v>65.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="AF31" s="5" t="n">
-        <v>65.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="AG31" s="5" t="n">
-        <v>58.2</v>
+        <v>58</v>
       </c>
       <c r="AH31" s="6" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
       <c r="AI31" s="7" t="n">
-        <v>52.4</v>
+        <v>52.2</v>
       </c>
       <c r="AJ31" s="7" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="AK31" s="7" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="AL31" s="7" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="AM31" s="8" t="n">
-        <v>36.9</v>
+        <v>36.6</v>
       </c>
       <c r="AN31" s="8" t="n">
-        <v>35.2</v>
+        <v>34.9</v>
       </c>
       <c r="AO31" s="8" t="n">
-        <v>35.2</v>
+        <v>34.9</v>
       </c>
       <c r="AP31" s="8" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="AQ31" s="8" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="AR31" s="8" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="AS31" s="8" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="AT31" s="8" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="AU31" s="8" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="AV31" s="8" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="AW31" s="8" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="AX31" s="8" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="AY31" s="8" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AZ31" s="3" t="n">
-        <v>234.77</v>
+        <v>234</v>
       </c>
       <c r="BA31" s="4" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="BB31" s="9" t="inlineStr">
         <is>
-          <t>MORE 6.5 | 58.2% | Edge +3.0</t>
+          <t>MORE 6.5 | 58.0% | Edge +3.0</t>
         </is>
       </c>
       <c r="BC31" s="4" t="inlineStr">
@@ -28671,13 +28671,13 @@
         <v>6.5</v>
       </c>
       <c r="BE31" s="3" t="n">
-        <v>58.2</v>
+        <v>58</v>
       </c>
       <c r="BF31" s="3" t="n">
-        <v>3.01</v>
+        <v>2.96</v>
       </c>
       <c r="BG31" s="3" t="n">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="BH31" s="4" t="inlineStr">
         <is>
@@ -29189,13 +29189,13 @@
         <v>6.61</v>
       </c>
       <c r="HK31" s="3" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="HL31" s="3" t="n">
-        <v>14.33</v>
+        <v>14.34</v>
       </c>
       <c r="HM31" s="3" t="n">
-        <v>18.78</v>
+        <v>18.06</v>
       </c>
       <c r="HN31" s="3" t="n">
         <v>4.71</v>
@@ -29214,94 +29214,94 @@
         </is>
       </c>
       <c r="HR31" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="HS31" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="HT31" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="HU31" s="3" t="n">
-        <v>74.7</v>
+        <v>74.5</v>
       </c>
       <c r="HV31" s="3" t="n">
-        <v>74.7</v>
+        <v>74.5</v>
       </c>
       <c r="HW31" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="HX31" s="3" t="n">
-        <v>61.4</v>
+        <v>61.2</v>
       </c>
       <c r="HY31" s="3" t="n">
-        <v>61.4</v>
+        <v>61.2</v>
       </c>
       <c r="HZ31" s="3" t="n">
-        <v>54.7</v>
+        <v>54.5</v>
       </c>
       <c r="IA31" s="3" t="n">
-        <v>49.9</v>
+        <v>49.7</v>
       </c>
       <c r="IB31" s="3" t="n">
-        <v>49.9</v>
+        <v>49.7</v>
       </c>
       <c r="IC31" s="3" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="ID31" s="3" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="IE31" s="3" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="IF31" s="3" t="n">
-        <v>36.9</v>
+        <v>36.6</v>
       </c>
       <c r="IG31" s="3" t="n">
-        <v>35.2</v>
+        <v>34.9</v>
       </c>
       <c r="IH31" s="3" t="n">
-        <v>35.2</v>
+        <v>34.9</v>
       </c>
       <c r="II31" s="3" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="IJ31" s="3" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="IK31" s="3" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="IL31" s="3" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="IM31" s="3" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="IN31" s="3" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="IO31" s="3" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="IP31" s="3" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="IQ31" s="3" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="IR31" s="3" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="IS31" s="3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="IT31" s="3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="IU31" s="3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="IV31" s="3" t="n">
         <v>7</v>
